--- a/Electricity-Diploma-Episode-Index.xlsx
+++ b/Electricity-Diploma-Episode-Index.xlsx
@@ -903,23 +903,91 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="21">
-      <c r="A7" s="30" t="n"/>
-      <c r="B7" s="30" t="n"/>
-      <c r="C7" s="30" t="n"/>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="31" t="n"/>
-      <c r="F7" s="30" t="n"/>
-      <c r="G7" s="30" t="n"/>
-      <c r="H7" s="30" t="n"/>
-      <c r="I7" s="30" t="n"/>
-      <c r="J7" s="30" t="n"/>
-      <c r="K7" s="30" t="n"/>
-      <c r="L7" s="30" t="n"/>
-      <c r="M7" s="30" t="n"/>
-      <c r="N7" s="30" t="n"/>
-      <c r="O7" s="30" t="n"/>
-      <c r="P7" s="30" t="n"/>
+    <row r="7" ht="165" customHeight="1" s="21">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>Designing a battery charge status monitoring circuit</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>Open README</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>Watch video</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>• Saturated transistor pulls its collector to ≈ 0 V (12 V / 0 V output)
+• Inverting transistor pair: Q1 on → Q2 off, Q1 off → Q2 on
+• Zener in the base path as a voltage-level detector
+• Designing resistor values from β_min, saturation factor and I_Z,min</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t>1. Transistor switch with 10 kΩ collector load (12 V / 0 V demo)
+2. Inverting pair with green/red LEDs driven by a push switch
+3. Battery monitor: 10 V Zener replaces the switch (green ≥ 10 V, red &lt; 10 V)</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="inlineStr">
+        <is>
+          <t>I_B = I_C / β_min = 10 mA / 200 = 50 µA
+I_B1 = 10 × 50 µA = 0.5 mA
+11 − V_Z − I_B1·R_B1 − 0.7 = 0 → R_B1 ≈ 600 Ω
+10 − 0.7 = I_B2(1 kΩ + R_B2), I_B2 = 200 µA → R_B2 ≈ 46 kΩ</t>
+        </is>
+      </c>
+      <c r="K7" s="25" t="inlineStr">
+        <is>
+          <t>2 × BC547B (β 200–450), BZX85C10 Zener (9.4–10.6 V), R_B1 = 677 Ω (600 Ω calc, 10 kΩ also works), R_B2 = 46 kΩ, 2 × 1 kΩ, red + green LED, 12 V battery</t>
+        </is>
+      </c>
+      <c r="L7" s="25" t="inlineStr">
+        <is>
+          <t>Not simulated yet</t>
+        </is>
+      </c>
+      <c r="M7" s="25" t="inlineStr">
+        <is>
+          <t>12 V, 11 V → green ✔; ≤ 10 V → red ✔; switch point ≈ 10.5 V (red starts glowing ≈ 10.6 V). With R_B1 = 10 kΩ still switches between 10 V and 11 V, lower battery drain.</t>
+        </is>
+      </c>
+      <c r="N7" s="25" t="inlineStr">
+        <is>
+          <t>README only (no media yet)</t>
+        </is>
+      </c>
+      <c r="O7" s="25" t="inlineStr">
+        <is>
+          <t>Adding one Zener to an inverting transistor pair turns it into a voltage monitor; swap the Zener for an LDR or thermistor and it becomes a light or temperature indicator. Calculated values are a starting point, then adjust by testing.</t>
+        </is>
+      </c>
+      <c r="P7" s="25" t="inlineStr">
+        <is>
+          <t>To do: Circuit Wizard sim sweeping 12 → 9 V to find my switch point; try R_B1 = 677 Ω vs 10 kΩ; try an LDR version (light/dark indicator).</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="21">
       <c r="A8" s="30" t="n"/>
@@ -1532,6 +1600,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" display="Watch video" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Electricity-Diploma-Episode-Index.xlsx
+++ b/Electricity-Diploma-Episode-Index.xlsx
@@ -919,7 +919,7 @@
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E7" s="28" t="n">
@@ -965,7 +965,9 @@
       </c>
       <c r="L7" s="25" t="inlineStr">
         <is>
-          <t>Not simulated yet</t>
+          <t>• R_B1 = 10 kΩ: 11 V → green, I_B1 = 52 µA, V_CE(Q1) = 101 mV ✔; 10 V → red 2.12 V, Zener 9.56 V at 0 A ✔; 8 V → red ✔
+• R_B1 = 677 Ω: 11 V → green, I_B1 = 638 µA, V_CE(Q1) = 24 mV ✔; 10 V → red ✔; 5 V → red dim
+• ≤ 3 V → neither LED lights</t>
         </is>
       </c>
       <c r="M7" s="25" t="inlineStr">
@@ -975,7 +977,7 @@
       </c>
       <c r="N7" s="25" t="inlineStr">
         <is>
-          <t>README only (no media yet)</t>
+          <t>1 simulation GIF + MP4: battery voltage sweep (10 kΩ vs 677 Ω)</t>
         </is>
       </c>
       <c r="O7" s="25" t="inlineStr">
@@ -985,7 +987,7 @@
       </c>
       <c r="P7" s="25" t="inlineStr">
         <is>
-          <t>To do: Circuit Wizard sim sweeping 12 → 9 V to find my switch point; try R_B1 = 677 Ω vs 10 kΩ; try an LDR version (light/dark indicator).</t>
+          <t>Sim used 1N4740 (10 V) instead of BZX85C10. To do: 0.1 V sweep between 10 and 11 V to find my switch point (video ≈ 10.5 V); try an LDR version (light/dark indicator).</t>
         </is>
       </c>
     </row>

--- a/Electricity-Diploma-Episode-Index.xlsx
+++ b/Electricity-Diploma-Episode-Index.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Episodes'!$A$4:$P$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Episodes'!$A$4:$P$200</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -609,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="20" min="1" max="1"/>
@@ -725,39 +725,199 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="165" customHeight="1" s="21">
+    <row r="5" ht="30" customHeight="1" s="21">
       <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Professional Electronic Design Course</t>
         </is>
       </c>
       <c r="B5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>Designing a simple circuit (closed / open) with full calculations</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="40" t="n"/>
+      <c r="G5" s="40" t="n"/>
+      <c r="H5" s="25" t="n"/>
+      <c r="I5" s="25" t="n"/>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="21">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>Designing a quiz board for two school teams</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="40" t="n"/>
+      <c r="G6" s="40" t="n"/>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="25" t="n"/>
+      <c r="L6" s="25" t="n"/>
+      <c r="M6" s="25" t="n"/>
+      <c r="N6" s="25" t="n"/>
+      <c r="O6" s="25" t="n"/>
+      <c r="P6" s="25" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1" s="21">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>Designing a large LED display board and choosing its component values</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="40" t="n"/>
+      <c r="G7" s="40" t="n"/>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="25" t="n"/>
+      <c r="L7" s="25" t="n"/>
+      <c r="M7" s="25" t="n"/>
+      <c r="N7" s="25" t="n"/>
+      <c r="O7" s="25" t="n"/>
+      <c r="P7" s="25" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="21">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>Designing a relay circuit for a contest where the fastest team wins</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="40" t="n"/>
+      <c r="G8" s="40" t="n"/>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="25" t="n"/>
+      <c r="L8" s="25" t="n"/>
+      <c r="M8" s="25" t="n"/>
+      <c r="N8" s="25" t="n"/>
+      <c r="O8" s="25" t="n"/>
+      <c r="P8" s="25" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="21">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>Designing a fish tank circuit based on sunlight intensity, with a light cell</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="40" t="n"/>
+      <c r="G9" s="40" t="n"/>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="25" t="n"/>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="25" t="n"/>
+      <c r="L9" s="25" t="n"/>
+      <c r="M9" s="25" t="n"/>
+      <c r="N9" s="25" t="n"/>
+      <c r="O9" s="25" t="n"/>
+      <c r="P9" s="25" t="n"/>
+    </row>
+    <row r="10" ht="165" customHeight="1" s="21">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>Various transistor circuits and circuit design for a light bulb factory</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="E5" s="28" t="n">
+      <c r="E10" s="28" t="n">
         <v>46311</v>
       </c>
-      <c r="F5" s="29" t="inlineStr">
+      <c r="F10" s="29" t="inlineStr">
         <is>
           <t>Open README</t>
         </is>
       </c>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="G10" s="29" t="inlineStr">
         <is>
           <t>Watch video</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H10" s="25" t="inlineStr">
         <is>
           <t>• Push-pull (complementary NPN/PNP) pair to steer current between two LEDs
 • Current-sensing transistor: sense resistor between base and emitter
@@ -765,14 +925,14 @@
 • Pull-up resistor as sensitivity calibration</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t>1. Push-pull LED selector (9 V)
 2. Current-sense LED indicator (12 V, 0.6 Ω)
 3. Light bulb tester: red if load &gt; 1 A, green if ≤ 1 A</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J10" s="25" t="inlineStr">
         <is>
           <t>V_BE = I_load × R_s
 I_trip ≈ 0.7 V / R_s
@@ -780,74 +940,74 @@
 I_LED ≈ (V_s − 0.7 − V_LED) / R</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t>BC547B (NPN) ×2, 2N5401 (PNP), R_s = 0.6 Ω (sim) / 3 × 1.5 Ω ∥ = 0.5 Ω (hardware), R3 = 4.7 kΩ pull-up, 2 × 220 Ω, red + green LED, 12 V supply</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L10" s="25" t="inlineStr">
         <is>
           <t>• Push-pull: only one LED lit at a time ✔
 • Current sensor: OFF at 1.0 A, dim at 1.1 A, bright at 1.2–1.5 A ✔
 • Bulb tester: green at 0 / 0.5 A ✔, red + green at 1.0–1.1 A (transition), red only at 1.2 A ✔</t>
         </is>
       </c>
-      <c r="M5" s="25" t="inlineStr">
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t>No load 0.038 A → green ✔
 Bulb 1: 1.6 A → red ✔
 Bulb 2: 0.19 A → green ✔</t>
         </is>
       </c>
-      <c r="N5" s="25" t="inlineStr">
+      <c r="N10" s="25" t="inlineStr">
         <is>
           <t>3 screenshots (.png), 3 simulation GIFs + MP4s: push-pull switching, current-sense threshold, bulb-tester sweep</t>
         </is>
       </c>
-      <c r="O5" s="25" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t>A resistor between base and emitter turns a transistor into a current-threshold detector; a complementary pair lets one signal choose between two loads; always check sense-resistor power.</t>
         </is>
       </c>
-      <c r="P5" s="25" t="inlineStr">
+      <c r="P10" s="25" t="inlineStr">
         <is>
           <t>Switch point in my sim is ≈ 1.2 A (video ≈ 1.1 A): try R3 = 5.6 kΩ or R4 ≈ 0.62–0.65 Ω. Sense resistors exceed ¼ W at 1.6 A → use ½–1 W.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="165" customHeight="1" s="21">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>Professional Electronic Design Course</t>
-        </is>
-      </c>
-      <c r="B6" s="26" t="n">
+    <row r="11" ht="165" customHeight="1" s="21">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>Designing a motor control switch monitoring circuit with LEDs</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E11" s="28" t="n">
         <v>46316</v>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>Open README</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>Watch video</t>
         </is>
       </c>
-      <c r="H6" s="25" t="inlineStr">
+      <c r="H11" s="25" t="inlineStr">
         <is>
           <t>• A lit LED holds ≈ 2–2.4 V across itself (acts like a regulator)
 • A parallel branch needing more than that voltage stays off
@@ -855,7 +1015,7 @@
 • Transistor as a short across an LED; shared vs. separate resistors</t>
         </is>
       </c>
-      <c r="I6" s="25" t="inlineStr">
+      <c r="I11" s="25" t="inlineStr">
         <is>
           <t>1. LED voltage vs. supply experiment (5–15 V)
 2. Red/green switch monitor with 3 series diodes
@@ -863,7 +1023,7 @@
 4. Same with an NPN transistor shorting the red LED (separate resistors)</t>
         </is>
       </c>
-      <c r="J6" s="25" t="inlineStr">
+      <c r="J11" s="25" t="inlineStr">
         <is>
           <t>V_branch = n × 0.7 V + V_F (diodes)
 V_branch = V_Z + V_F (Zener)
@@ -871,71 +1031,71 @@
 V_green = V_s − I × R_shared</t>
         </is>
       </c>
-      <c r="K6" s="25" t="inlineStr">
+      <c r="K11" s="25" t="inlineStr">
         <is>
           <t>12 V supply, DC motor, SPST switch, 3 × silicon diode, 1N751 5.1 V Zener, NPN transistor, 1 kΩ resistors, red + green LED</t>
         </is>
       </c>
-      <c r="L6" s="25" t="inlineStr">
+      <c r="L11" s="25" t="inlineStr">
         <is>
           <t>• 3 diodes: open → red 2.16 V, 8.08 mA ✔; closed → green 2.31 V, red 0.94 V (off) ✔
 • Zener: open → red on, Zener 5.11 V, 5.21 mA ✔; closed → green ≈ 2.45 V, Zener 4.68 V (off) ✔</t>
         </is>
       </c>
-      <c r="M6" s="25" t="inlineStr">
+      <c r="M11" s="25" t="inlineStr">
         <is>
           <t>All three boards switch red ↔ green correctly with a lamp load. Diodes stay cool, Zener slightly warm, transistor design's resistor gets warm.</t>
         </is>
       </c>
-      <c r="N6" s="25" t="inlineStr">
+      <c r="N11" s="25" t="inlineStr">
         <is>
           <t>3 simulation GIFs + MP4s: three-diodes switching, Zener first press, Zener toggling</t>
         </is>
       </c>
-      <c r="O6" s="25" t="inlineStr">
+      <c r="O11" s="25" t="inlineStr">
         <is>
           <t>A lit LED clamps anything in parallel to ≈ 2 V, so making the other branch need more voltage forces it off. A transistor short works too, but each LED then needs its own resistor.</t>
         </is>
       </c>
-      <c r="P6" s="25" t="inlineStr">
+      <c r="P11" s="25" t="inlineStr">
         <is>
           <t>Transistor design: shared 1 kΩ dropped ≈ 10.8 V, leaving ≈ 1.2–1.6 V for green (off) → fixed with separate resistors. No transistor-design sim recorded yet.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="165" customHeight="1" s="21">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>Professional Electronic Design Course</t>
-        </is>
-      </c>
-      <c r="B7" s="26" t="n">
+    <row r="12" ht="165" customHeight="1" s="21">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>Designing a battery charge status monitoring circuit</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E12" s="28" t="n">
         <v>46319</v>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>Open README</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>Watch video</t>
         </is>
       </c>
-      <c r="H7" s="25" t="inlineStr">
+      <c r="H12" s="25" t="inlineStr">
         <is>
           <t>• Saturated transistor pulls its collector to ≈ 0 V (12 V / 0 V output)
 • Inverting transistor pair: Q1 on → Q2 off, Q1 off → Q2 on
@@ -943,14 +1103,14 @@
 • Designing resistor values from β_min, saturation factor and I_Z,min</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I12" s="25" t="inlineStr">
         <is>
           <t>1. Transistor switch with 10 kΩ collector load (12 V / 0 V demo)
 2. Inverting pair with green/red LEDs driven by a push switch
 3. Battery monitor: 10 V Zener replaces the switch (green ≥ 10 V, red &lt; 10 V)</t>
         </is>
       </c>
-      <c r="J7" s="25" t="inlineStr">
+      <c r="J12" s="25" t="inlineStr">
         <is>
           <t>I_B = I_C / β_min = 10 mA / 200 = 50 µA
 I_B1 = 10 × 50 µA = 0.5 mA
@@ -958,652 +1118,2202 @@
 10 − 0.7 = I_B2(1 kΩ + R_B2), I_B2 = 200 µA → R_B2 ≈ 46 kΩ</t>
         </is>
       </c>
-      <c r="K7" s="25" t="inlineStr">
+      <c r="K12" s="25" t="inlineStr">
         <is>
           <t>2 × BC547B (β 200–450), BZX85C10 Zener (9.4–10.6 V), R_B1 = 677 Ω (600 Ω calc, 10 kΩ also works), R_B2 = 46 kΩ, 2 × 1 kΩ, red + green LED, 12 V battery</t>
         </is>
       </c>
-      <c r="L7" s="25" t="inlineStr">
+      <c r="L12" s="25" t="inlineStr">
         <is>
           <t>• R_B1 = 10 kΩ: 11 V → green, I_B1 = 52 µA, V_CE(Q1) = 101 mV ✔; 10 V → red 2.12 V, Zener 9.56 V at 0 A ✔; 8 V → red ✔
 • R_B1 = 677 Ω: 11 V → green, I_B1 = 638 µA, V_CE(Q1) = 24 mV ✔; 10 V → red ✔; 5 V → red dim
 • ≤ 3 V → neither LED lights</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M12" s="25" t="inlineStr">
         <is>
           <t>12 V, 11 V → green ✔; ≤ 10 V → red ✔; switch point ≈ 10.5 V (red starts glowing ≈ 10.6 V). With R_B1 = 10 kΩ still switches between 10 V and 11 V, lower battery drain.</t>
         </is>
       </c>
-      <c r="N7" s="25" t="inlineStr">
+      <c r="N12" s="25" t="inlineStr">
         <is>
           <t>1 simulation GIF + MP4: battery voltage sweep (10 kΩ vs 677 Ω)</t>
         </is>
       </c>
-      <c r="O7" s="25" t="inlineStr">
+      <c r="O12" s="25" t="inlineStr">
         <is>
           <t>Adding one Zener to an inverting transistor pair turns it into a voltage monitor; swap the Zener for an LDR or thermistor and it becomes a light or temperature indicator. Calculated values are a starting point, then adjust by testing.</t>
         </is>
       </c>
-      <c r="P7" s="25" t="inlineStr">
+      <c r="P12" s="25" t="inlineStr">
         <is>
           <t>Sim used 1N4740 (10 V) instead of BZX85C10. To do: 0.1 V sweep between 10 and 11 V to find my switch point (video ≈ 10.5 V); try an LDR version (light/dark indicator).</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="21">
-      <c r="A8" s="30" t="n"/>
-      <c r="B8" s="30" t="n"/>
-      <c r="C8" s="30" t="n"/>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="31" t="n"/>
-      <c r="F8" s="30" t="n"/>
-      <c r="G8" s="30" t="n"/>
-      <c r="H8" s="30" t="n"/>
-      <c r="I8" s="30" t="n"/>
-      <c r="J8" s="30" t="n"/>
-      <c r="K8" s="30" t="n"/>
-      <c r="L8" s="30" t="n"/>
-      <c r="M8" s="30" t="n"/>
-      <c r="N8" s="30" t="n"/>
-      <c r="O8" s="30" t="n"/>
-      <c r="P8" s="30" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="21">
-      <c r="A9" s="30" t="n"/>
-      <c r="B9" s="30" t="n"/>
-      <c r="C9" s="30" t="n"/>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="31" t="n"/>
-      <c r="F9" s="30" t="n"/>
-      <c r="G9" s="30" t="n"/>
-      <c r="H9" s="30" t="n"/>
-      <c r="I9" s="30" t="n"/>
-      <c r="J9" s="30" t="n"/>
-      <c r="K9" s="30" t="n"/>
-      <c r="L9" s="30" t="n"/>
-      <c r="M9" s="30" t="n"/>
-      <c r="N9" s="30" t="n"/>
-      <c r="O9" s="30" t="n"/>
-      <c r="P9" s="30" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="21">
-      <c r="A10" s="30" t="n"/>
-      <c r="B10" s="30" t="n"/>
-      <c r="C10" s="30" t="n"/>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="31" t="n"/>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="n"/>
-      <c r="H10" s="30" t="n"/>
-      <c r="I10" s="30" t="n"/>
-      <c r="J10" s="30" t="n"/>
-      <c r="K10" s="30" t="n"/>
-      <c r="L10" s="30" t="n"/>
-      <c r="M10" s="30" t="n"/>
-      <c r="N10" s="30" t="n"/>
-      <c r="O10" s="30" t="n"/>
-      <c r="P10" s="30" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="21">
-      <c r="A11" s="30" t="n"/>
-      <c r="B11" s="30" t="n"/>
-      <c r="C11" s="30" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="31" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="30" t="n"/>
-      <c r="I11" s="30" t="n"/>
-      <c r="J11" s="30" t="n"/>
-      <c r="K11" s="30" t="n"/>
-      <c r="L11" s="30" t="n"/>
-      <c r="M11" s="30" t="n"/>
-      <c r="N11" s="30" t="n"/>
-      <c r="O11" s="30" t="n"/>
-      <c r="P11" s="30" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="21">
-      <c r="A12" s="30" t="n"/>
-      <c r="B12" s="30" t="n"/>
-      <c r="C12" s="30" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="31" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="30" t="n"/>
-      <c r="H12" s="30" t="n"/>
-      <c r="I12" s="30" t="n"/>
-      <c r="J12" s="30" t="n"/>
-      <c r="K12" s="30" t="n"/>
-      <c r="L12" s="30" t="n"/>
-      <c r="M12" s="30" t="n"/>
-      <c r="N12" s="30" t="n"/>
-      <c r="O12" s="30" t="n"/>
-      <c r="P12" s="30" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="21">
-      <c r="A13" s="30" t="n"/>
-      <c r="B13" s="30" t="n"/>
-      <c r="C13" s="30" t="n"/>
-      <c r="D13" s="30" t="n"/>
-      <c r="E13" s="31" t="n"/>
-      <c r="F13" s="30" t="n"/>
-      <c r="G13" s="30" t="n"/>
-      <c r="H13" s="30" t="n"/>
-      <c r="I13" s="30" t="n"/>
-      <c r="J13" s="30" t="n"/>
-      <c r="K13" s="30" t="n"/>
-      <c r="L13" s="30" t="n"/>
-      <c r="M13" s="30" t="n"/>
-      <c r="N13" s="30" t="n"/>
-      <c r="O13" s="30" t="n"/>
-      <c r="P13" s="30" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="21">
-      <c r="A14" s="30" t="n"/>
-      <c r="B14" s="30" t="n"/>
-      <c r="C14" s="30" t="n"/>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="31" t="n"/>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="30" t="n"/>
-      <c r="H14" s="30" t="n"/>
-      <c r="I14" s="30" t="n"/>
-      <c r="J14" s="30" t="n"/>
-      <c r="K14" s="30" t="n"/>
-      <c r="L14" s="30" t="n"/>
-      <c r="M14" s="30" t="n"/>
-      <c r="N14" s="30" t="n"/>
-      <c r="O14" s="30" t="n"/>
-      <c r="P14" s="30" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="21">
-      <c r="A15" s="30" t="n"/>
-      <c r="B15" s="30" t="n"/>
-      <c r="C15" s="30" t="n"/>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="31" t="n"/>
-      <c r="F15" s="30" t="n"/>
-      <c r="G15" s="30" t="n"/>
-      <c r="H15" s="30" t="n"/>
-      <c r="I15" s="30" t="n"/>
-      <c r="J15" s="30" t="n"/>
-      <c r="K15" s="30" t="n"/>
-      <c r="L15" s="30" t="n"/>
-      <c r="M15" s="30" t="n"/>
-      <c r="N15" s="30" t="n"/>
-      <c r="O15" s="30" t="n"/>
-      <c r="P15" s="30" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="21">
-      <c r="A16" s="30" t="n"/>
-      <c r="B16" s="30" t="n"/>
-      <c r="C16" s="30" t="n"/>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="31" t="n"/>
-      <c r="F16" s="30" t="n"/>
-      <c r="G16" s="30" t="n"/>
-      <c r="H16" s="30" t="n"/>
-      <c r="I16" s="30" t="n"/>
-      <c r="J16" s="30" t="n"/>
-      <c r="K16" s="30" t="n"/>
-      <c r="L16" s="30" t="n"/>
-      <c r="M16" s="30" t="n"/>
-      <c r="N16" s="30" t="n"/>
-      <c r="O16" s="30" t="n"/>
-      <c r="P16" s="30" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="21">
-      <c r="A17" s="30" t="n"/>
-      <c r="B17" s="30" t="n"/>
-      <c r="C17" s="30" t="n"/>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="31" t="n"/>
-      <c r="F17" s="30" t="n"/>
-      <c r="G17" s="30" t="n"/>
-      <c r="H17" s="30" t="n"/>
-      <c r="I17" s="30" t="n"/>
-      <c r="J17" s="30" t="n"/>
-      <c r="K17" s="30" t="n"/>
-      <c r="L17" s="30" t="n"/>
-      <c r="M17" s="30" t="n"/>
-      <c r="N17" s="30" t="n"/>
-      <c r="O17" s="30" t="n"/>
-      <c r="P17" s="30" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="21">
-      <c r="A18" s="30" t="n"/>
-      <c r="B18" s="30" t="n"/>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="31" t="n"/>
-      <c r="F18" s="30" t="n"/>
-      <c r="G18" s="30" t="n"/>
-      <c r="H18" s="30" t="n"/>
-      <c r="I18" s="30" t="n"/>
-      <c r="J18" s="30" t="n"/>
-      <c r="K18" s="30" t="n"/>
-      <c r="L18" s="30" t="n"/>
-      <c r="M18" s="30" t="n"/>
-      <c r="N18" s="30" t="n"/>
-      <c r="O18" s="30" t="n"/>
-      <c r="P18" s="30" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="21">
-      <c r="A19" s="30" t="n"/>
-      <c r="B19" s="30" t="n"/>
-      <c r="C19" s="30" t="n"/>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="31" t="n"/>
-      <c r="F19" s="30" t="n"/>
-      <c r="G19" s="30" t="n"/>
-      <c r="H19" s="30" t="n"/>
-      <c r="I19" s="30" t="n"/>
-      <c r="J19" s="30" t="n"/>
-      <c r="K19" s="30" t="n"/>
-      <c r="L19" s="30" t="n"/>
-      <c r="M19" s="30" t="n"/>
-      <c r="N19" s="30" t="n"/>
-      <c r="O19" s="30" t="n"/>
-      <c r="P19" s="30" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="21">
-      <c r="A20" s="30" t="n"/>
-      <c r="B20" s="30" t="n"/>
-      <c r="C20" s="30" t="n"/>
-      <c r="D20" s="30" t="n"/>
-      <c r="E20" s="31" t="n"/>
-      <c r="F20" s="30" t="n"/>
-      <c r="G20" s="30" t="n"/>
-      <c r="H20" s="30" t="n"/>
-      <c r="I20" s="30" t="n"/>
-      <c r="J20" s="30" t="n"/>
-      <c r="K20" s="30" t="n"/>
-      <c r="L20" s="30" t="n"/>
-      <c r="M20" s="30" t="n"/>
-      <c r="N20" s="30" t="n"/>
-      <c r="O20" s="30" t="n"/>
-      <c r="P20" s="30" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="21">
-      <c r="A21" s="30" t="n"/>
-      <c r="B21" s="30" t="n"/>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="31" t="n"/>
-      <c r="F21" s="30" t="n"/>
-      <c r="G21" s="30" t="n"/>
-      <c r="H21" s="30" t="n"/>
-      <c r="I21" s="30" t="n"/>
-      <c r="J21" s="30" t="n"/>
-      <c r="K21" s="30" t="n"/>
-      <c r="L21" s="30" t="n"/>
-      <c r="M21" s="30" t="n"/>
-      <c r="N21" s="30" t="n"/>
-      <c r="O21" s="30" t="n"/>
-      <c r="P21" s="30" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="21">
-      <c r="A22" s="30" t="n"/>
-      <c r="B22" s="30" t="n"/>
-      <c r="C22" s="30" t="n"/>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="31" t="n"/>
-      <c r="F22" s="30" t="n"/>
-      <c r="G22" s="30" t="n"/>
-      <c r="H22" s="30" t="n"/>
-      <c r="I22" s="30" t="n"/>
-      <c r="J22" s="30" t="n"/>
-      <c r="K22" s="30" t="n"/>
-      <c r="L22" s="30" t="n"/>
-      <c r="M22" s="30" t="n"/>
-      <c r="N22" s="30" t="n"/>
-      <c r="O22" s="30" t="n"/>
-      <c r="P22" s="30" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="21">
-      <c r="A23" s="30" t="n"/>
-      <c r="B23" s="30" t="n"/>
-      <c r="C23" s="30" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="31" t="n"/>
-      <c r="F23" s="30" t="n"/>
-      <c r="G23" s="30" t="n"/>
-      <c r="H23" s="30" t="n"/>
-      <c r="I23" s="30" t="n"/>
-      <c r="J23" s="30" t="n"/>
-      <c r="K23" s="30" t="n"/>
-      <c r="L23" s="30" t="n"/>
-      <c r="M23" s="30" t="n"/>
-      <c r="N23" s="30" t="n"/>
-      <c r="O23" s="30" t="n"/>
-      <c r="P23" s="30" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="21">
-      <c r="A24" s="30" t="n"/>
-      <c r="B24" s="30" t="n"/>
-      <c r="C24" s="30" t="n"/>
-      <c r="D24" s="30" t="n"/>
-      <c r="E24" s="31" t="n"/>
-      <c r="F24" s="30" t="n"/>
-      <c r="G24" s="30" t="n"/>
-      <c r="H24" s="30" t="n"/>
-      <c r="I24" s="30" t="n"/>
-      <c r="J24" s="30" t="n"/>
-      <c r="K24" s="30" t="n"/>
-      <c r="L24" s="30" t="n"/>
-      <c r="M24" s="30" t="n"/>
-      <c r="N24" s="30" t="n"/>
-      <c r="O24" s="30" t="n"/>
-      <c r="P24" s="30" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="21">
-      <c r="A25" s="30" t="n"/>
-      <c r="B25" s="30" t="n"/>
-      <c r="C25" s="30" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="31" t="n"/>
-      <c r="F25" s="30" t="n"/>
-      <c r="G25" s="30" t="n"/>
-      <c r="H25" s="30" t="n"/>
-      <c r="I25" s="30" t="n"/>
-      <c r="J25" s="30" t="n"/>
-      <c r="K25" s="30" t="n"/>
-      <c r="L25" s="30" t="n"/>
-      <c r="M25" s="30" t="n"/>
-      <c r="N25" s="30" t="n"/>
-      <c r="O25" s="30" t="n"/>
-      <c r="P25" s="30" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="21">
-      <c r="A26" s="30" t="n"/>
-      <c r="B26" s="30" t="n"/>
-      <c r="C26" s="30" t="n"/>
-      <c r="D26" s="30" t="n"/>
-      <c r="E26" s="31" t="n"/>
-      <c r="F26" s="30" t="n"/>
-      <c r="G26" s="30" t="n"/>
-      <c r="H26" s="30" t="n"/>
-      <c r="I26" s="30" t="n"/>
-      <c r="J26" s="30" t="n"/>
-      <c r="K26" s="30" t="n"/>
-      <c r="L26" s="30" t="n"/>
-      <c r="M26" s="30" t="n"/>
-      <c r="N26" s="30" t="n"/>
-      <c r="O26" s="30" t="n"/>
-      <c r="P26" s="30" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="21">
-      <c r="A27" s="30" t="n"/>
-      <c r="B27" s="30" t="n"/>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="30" t="n"/>
-      <c r="G27" s="30" t="n"/>
-      <c r="H27" s="30" t="n"/>
-      <c r="I27" s="30" t="n"/>
-      <c r="J27" s="30" t="n"/>
-      <c r="K27" s="30" t="n"/>
-      <c r="L27" s="30" t="n"/>
-      <c r="M27" s="30" t="n"/>
-      <c r="N27" s="30" t="n"/>
-      <c r="O27" s="30" t="n"/>
-      <c r="P27" s="30" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="21">
-      <c r="A28" s="30" t="n"/>
-      <c r="B28" s="30" t="n"/>
-      <c r="C28" s="30" t="n"/>
-      <c r="D28" s="30" t="n"/>
-      <c r="E28" s="31" t="n"/>
-      <c r="F28" s="30" t="n"/>
-      <c r="G28" s="30" t="n"/>
-      <c r="H28" s="30" t="n"/>
-      <c r="I28" s="30" t="n"/>
-      <c r="J28" s="30" t="n"/>
-      <c r="K28" s="30" t="n"/>
-      <c r="L28" s="30" t="n"/>
-      <c r="M28" s="30" t="n"/>
-      <c r="N28" s="30" t="n"/>
-      <c r="O28" s="30" t="n"/>
-      <c r="P28" s="30" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="21">
-      <c r="A29" s="30" t="n"/>
-      <c r="B29" s="30" t="n"/>
-      <c r="C29" s="30" t="n"/>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="31" t="n"/>
-      <c r="F29" s="30" t="n"/>
-      <c r="G29" s="30" t="n"/>
-      <c r="H29" s="30" t="n"/>
-      <c r="I29" s="30" t="n"/>
-      <c r="J29" s="30" t="n"/>
-      <c r="K29" s="30" t="n"/>
-      <c r="L29" s="30" t="n"/>
-      <c r="M29" s="30" t="n"/>
-      <c r="N29" s="30" t="n"/>
-      <c r="O29" s="30" t="n"/>
-      <c r="P29" s="30" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="21">
-      <c r="A30" s="30" t="n"/>
-      <c r="B30" s="30" t="n"/>
-      <c r="C30" s="30" t="n"/>
-      <c r="D30" s="30" t="n"/>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="30" t="n"/>
-      <c r="G30" s="30" t="n"/>
-      <c r="H30" s="30" t="n"/>
-      <c r="I30" s="30" t="n"/>
-      <c r="J30" s="30" t="n"/>
-      <c r="K30" s="30" t="n"/>
-      <c r="L30" s="30" t="n"/>
-      <c r="M30" s="30" t="n"/>
-      <c r="N30" s="30" t="n"/>
-      <c r="O30" s="30" t="n"/>
-      <c r="P30" s="30" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="21">
-      <c r="A31" s="30" t="n"/>
-      <c r="B31" s="30" t="n"/>
-      <c r="C31" s="30" t="n"/>
-      <c r="D31" s="30" t="n"/>
-      <c r="E31" s="31" t="n"/>
-      <c r="F31" s="30" t="n"/>
-      <c r="G31" s="30" t="n"/>
-      <c r="H31" s="30" t="n"/>
-      <c r="I31" s="30" t="n"/>
-      <c r="J31" s="30" t="n"/>
-      <c r="K31" s="30" t="n"/>
-      <c r="L31" s="30" t="n"/>
-      <c r="M31" s="30" t="n"/>
-      <c r="N31" s="30" t="n"/>
-      <c r="O31" s="30" t="n"/>
-      <c r="P31" s="30" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="21">
-      <c r="A32" s="30" t="n"/>
-      <c r="B32" s="30" t="n"/>
-      <c r="C32" s="30" t="n"/>
-      <c r="D32" s="30" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="30" t="n"/>
-      <c r="G32" s="30" t="n"/>
-      <c r="H32" s="30" t="n"/>
-      <c r="I32" s="30" t="n"/>
-      <c r="J32" s="30" t="n"/>
-      <c r="K32" s="30" t="n"/>
-      <c r="L32" s="30" t="n"/>
-      <c r="M32" s="30" t="n"/>
-      <c r="N32" s="30" t="n"/>
-      <c r="O32" s="30" t="n"/>
-      <c r="P32" s="30" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="21">
-      <c r="A33" s="30" t="n"/>
-      <c r="B33" s="30" t="n"/>
-      <c r="C33" s="30" t="n"/>
-      <c r="D33" s="30" t="n"/>
-      <c r="E33" s="31" t="n"/>
-      <c r="F33" s="30" t="n"/>
-      <c r="G33" s="30" t="n"/>
-      <c r="H33" s="30" t="n"/>
-      <c r="I33" s="30" t="n"/>
-      <c r="J33" s="30" t="n"/>
-      <c r="K33" s="30" t="n"/>
-      <c r="L33" s="30" t="n"/>
-      <c r="M33" s="30" t="n"/>
-      <c r="N33" s="30" t="n"/>
-      <c r="O33" s="30" t="n"/>
-      <c r="P33" s="30" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="21">
-      <c r="A34" s="30" t="n"/>
-      <c r="B34" s="30" t="n"/>
-      <c r="C34" s="30" t="n"/>
-      <c r="D34" s="30" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="30" t="n"/>
-      <c r="G34" s="30" t="n"/>
-      <c r="H34" s="30" t="n"/>
-      <c r="I34" s="30" t="n"/>
-      <c r="J34" s="30" t="n"/>
-      <c r="K34" s="30" t="n"/>
-      <c r="L34" s="30" t="n"/>
-      <c r="M34" s="30" t="n"/>
-      <c r="N34" s="30" t="n"/>
-      <c r="O34" s="30" t="n"/>
-      <c r="P34" s="30" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="21">
-      <c r="A35" s="30" t="n"/>
-      <c r="B35" s="30" t="n"/>
-      <c r="C35" s="30" t="n"/>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="30" t="n"/>
-      <c r="G35" s="30" t="n"/>
-      <c r="H35" s="30" t="n"/>
-      <c r="I35" s="30" t="n"/>
-      <c r="J35" s="30" t="n"/>
-      <c r="K35" s="30" t="n"/>
-      <c r="L35" s="30" t="n"/>
-      <c r="M35" s="30" t="n"/>
-      <c r="N35" s="30" t="n"/>
-      <c r="O35" s="30" t="n"/>
-      <c r="P35" s="30" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="21">
-      <c r="A36" s="30" t="n"/>
-      <c r="B36" s="30" t="n"/>
-      <c r="C36" s="30" t="n"/>
-      <c r="D36" s="30" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="30" t="n"/>
-      <c r="G36" s="30" t="n"/>
-      <c r="H36" s="30" t="n"/>
-      <c r="I36" s="30" t="n"/>
-      <c r="J36" s="30" t="n"/>
-      <c r="K36" s="30" t="n"/>
-      <c r="L36" s="30" t="n"/>
-      <c r="M36" s="30" t="n"/>
-      <c r="N36" s="30" t="n"/>
-      <c r="O36" s="30" t="n"/>
-      <c r="P36" s="30" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="21">
-      <c r="A37" s="30" t="n"/>
-      <c r="B37" s="30" t="n"/>
-      <c r="C37" s="30" t="n"/>
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="31" t="n"/>
-      <c r="F37" s="30" t="n"/>
-      <c r="G37" s="30" t="n"/>
-      <c r="H37" s="30" t="n"/>
-      <c r="I37" s="30" t="n"/>
-      <c r="J37" s="30" t="n"/>
-      <c r="K37" s="30" t="n"/>
-      <c r="L37" s="30" t="n"/>
-      <c r="M37" s="30" t="n"/>
-      <c r="N37" s="30" t="n"/>
-      <c r="O37" s="30" t="n"/>
-      <c r="P37" s="30" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="21">
-      <c r="A38" s="30" t="n"/>
-      <c r="B38" s="30" t="n"/>
-      <c r="C38" s="30" t="n"/>
-      <c r="D38" s="30" t="n"/>
-      <c r="E38" s="31" t="n"/>
-      <c r="F38" s="30" t="n"/>
-      <c r="G38" s="30" t="n"/>
-      <c r="H38" s="30" t="n"/>
-      <c r="I38" s="30" t="n"/>
-      <c r="J38" s="30" t="n"/>
-      <c r="K38" s="30" t="n"/>
-      <c r="L38" s="30" t="n"/>
-      <c r="M38" s="30" t="n"/>
-      <c r="N38" s="30" t="n"/>
-      <c r="O38" s="30" t="n"/>
-      <c r="P38" s="30" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="21">
-      <c r="A39" s="30" t="n"/>
-      <c r="B39" s="30" t="n"/>
-      <c r="C39" s="30" t="n"/>
-      <c r="D39" s="30" t="n"/>
-      <c r="E39" s="31" t="n"/>
-      <c r="F39" s="30" t="n"/>
-      <c r="G39" s="30" t="n"/>
-      <c r="H39" s="30" t="n"/>
-      <c r="I39" s="30" t="n"/>
-      <c r="J39" s="30" t="n"/>
-      <c r="K39" s="30" t="n"/>
-      <c r="L39" s="30" t="n"/>
-      <c r="M39" s="30" t="n"/>
-      <c r="N39" s="30" t="n"/>
-      <c r="O39" s="30" t="n"/>
-      <c r="P39" s="30" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="21">
-      <c r="A40" s="30" t="n"/>
-      <c r="B40" s="30" t="n"/>
-      <c r="C40" s="30" t="n"/>
-      <c r="D40" s="30" t="n"/>
-      <c r="E40" s="31" t="n"/>
-      <c r="F40" s="30" t="n"/>
-      <c r="G40" s="30" t="n"/>
-      <c r="H40" s="30" t="n"/>
-      <c r="I40" s="30" t="n"/>
-      <c r="J40" s="30" t="n"/>
-      <c r="K40" s="30" t="n"/>
-      <c r="L40" s="30" t="n"/>
-      <c r="M40" s="30" t="n"/>
-      <c r="N40" s="30" t="n"/>
-      <c r="O40" s="30" t="n"/>
-      <c r="P40" s="30" t="n"/>
+    <row r="13" ht="30" customHeight="1" s="21">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>Designing a car-factory panel to control the cooling fan</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="n"/>
+      <c r="F13" s="40" t="n"/>
+      <c r="G13" s="40" t="n"/>
+      <c r="H13" s="25" t="n"/>
+      <c r="I13" s="25" t="n"/>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="25" t="n"/>
+      <c r="L13" s="25" t="n"/>
+      <c r="M13" s="25" t="n"/>
+      <c r="N13" s="25" t="n"/>
+      <c r="O13" s="25" t="n"/>
+      <c r="P13" s="25" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="21">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>Designing a car-factory circuit for testing fans</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="40" t="n"/>
+      <c r="G14" s="40" t="n"/>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="25" t="n"/>
+      <c r="L14" s="25" t="n"/>
+      <c r="M14" s="25" t="n"/>
+      <c r="N14" s="25" t="n"/>
+      <c r="O14" s="25" t="n"/>
+      <c r="P14" s="25" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="21">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>Designing a useless machine motor circuit</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="25" t="n"/>
+      <c r="I15" s="25" t="n"/>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="25" t="n"/>
+      <c r="L15" s="25" t="n"/>
+      <c r="M15" s="25" t="n"/>
+      <c r="N15" s="25" t="n"/>
+      <c r="O15" s="25" t="n"/>
+      <c r="P15" s="25" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="21">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>Designing a secret-code circuit without programming</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="40" t="n"/>
+      <c r="G16" s="40" t="n"/>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="25" t="n"/>
+      <c r="L16" s="25" t="n"/>
+      <c r="M16" s="25" t="n"/>
+      <c r="N16" s="25" t="n"/>
+      <c r="O16" s="25" t="n"/>
+      <c r="P16" s="25" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="21">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>Designing an interactive smart board for schools without programming</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="40" t="n"/>
+      <c r="G17" s="40" t="n"/>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="25" t="n"/>
+      <c r="L17" s="25" t="n"/>
+      <c r="M17" s="25" t="n"/>
+      <c r="N17" s="25" t="n"/>
+      <c r="O17" s="25" t="n"/>
+      <c r="P17" s="25" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="21">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>Designing a joystick circuit that controls a motor for a toy factory</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="40" t="n"/>
+      <c r="G18" s="40" t="n"/>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="25" t="n"/>
+      <c r="L18" s="25" t="n"/>
+      <c r="M18" s="25" t="n"/>
+      <c r="N18" s="25" t="n"/>
+      <c r="O18" s="25" t="n"/>
+      <c r="P18" s="25" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="21">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
+        <is>
+          <t>Designing a one-press electric drill circuit with a relay</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="40" t="n"/>
+      <c r="G19" s="40" t="n"/>
+      <c r="H19" s="25" t="n"/>
+      <c r="I19" s="25" t="n"/>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="25" t="n"/>
+      <c r="L19" s="25" t="n"/>
+      <c r="M19" s="25" t="n"/>
+      <c r="N19" s="25" t="n"/>
+      <c r="O19" s="25" t="n"/>
+      <c r="P19" s="25" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="21">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
+        <is>
+          <t>Designing a transistor latch circuit with a delay that avoids many problems</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="n"/>
+      <c r="F20" s="40" t="n"/>
+      <c r="G20" s="40" t="n"/>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="25" t="n"/>
+      <c r="L20" s="25" t="n"/>
+      <c r="M20" s="25" t="n"/>
+      <c r="N20" s="25" t="n"/>
+      <c r="O20" s="25" t="n"/>
+      <c r="P20" s="25" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>Designing a smart circuit for a mailbox in front of the house</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="n"/>
+      <c r="F21" s="40" t="n"/>
+      <c r="G21" s="40" t="n"/>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="25" t="n"/>
+      <c r="L21" s="25" t="n"/>
+      <c r="M21" s="25" t="n"/>
+      <c r="N21" s="25" t="n"/>
+      <c r="O21" s="25" t="n"/>
+      <c r="P21" s="25" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1" s="21">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>Designing a one-press circuit: problems and solutions</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="40" t="n"/>
+      <c r="G22" s="40" t="n"/>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="25" t="n"/>
+      <c r="L22" s="25" t="n"/>
+      <c r="M22" s="25" t="n"/>
+      <c r="N22" s="25" t="n"/>
+      <c r="O22" s="25" t="n"/>
+      <c r="P22" s="25" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1" s="21">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" s="25" t="inlineStr">
+        <is>
+          <t>Analysing three transistor circuits to learn from them</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E23" s="28" t="n"/>
+      <c r="F23" s="40" t="n"/>
+      <c r="G23" s="40" t="n"/>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="25" t="n"/>
+      <c r="L23" s="25" t="n"/>
+      <c r="M23" s="25" t="n"/>
+      <c r="N23" s="25" t="n"/>
+      <c r="O23" s="25" t="n"/>
+      <c r="P23" s="25" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1" s="21">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" s="25" t="inlineStr">
+        <is>
+          <t>The flip-flop capacitor as an oscillator, and designing a status indicator</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E24" s="28" t="n"/>
+      <c r="F24" s="40" t="n"/>
+      <c r="G24" s="40" t="n"/>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="25" t="n"/>
+      <c r="L24" s="25" t="n"/>
+      <c r="M24" s="25" t="n"/>
+      <c r="N24" s="25" t="n"/>
+      <c r="O24" s="25" t="n"/>
+      <c r="P24" s="25" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1" s="21">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" s="25" t="inlineStr">
+        <is>
+          <t>Designing a random-selection circuit using the oscillator</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="n"/>
+      <c r="F25" s="40" t="n"/>
+      <c r="G25" s="40" t="n"/>
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="25" t="n"/>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="25" t="n"/>
+      <c r="L25" s="25" t="n"/>
+      <c r="M25" s="25" t="n"/>
+      <c r="N25" s="25" t="n"/>
+      <c r="O25" s="25" t="n"/>
+      <c r="P25" s="25" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1" s="21">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>Designing a boost circuit for an efficient torch with a small battery</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="40" t="n"/>
+      <c r="G26" s="40" t="n"/>
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="25" t="n"/>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="25" t="n"/>
+      <c r="L26" s="25" t="n"/>
+      <c r="M26" s="25" t="n"/>
+      <c r="N26" s="25" t="n"/>
+      <c r="O26" s="25" t="n"/>
+      <c r="P26" s="25" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1" s="21">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>Designing a sequential oscillator circuit for decorative lights</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E27" s="28" t="n"/>
+      <c r="F27" s="40" t="n"/>
+      <c r="G27" s="40" t="n"/>
+      <c r="H27" s="25" t="n"/>
+      <c r="I27" s="25" t="n"/>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="25" t="n"/>
+      <c r="L27" s="25" t="n"/>
+      <c r="M27" s="25" t="n"/>
+      <c r="N27" s="25" t="n"/>
+      <c r="O27" s="25" t="n"/>
+      <c r="P27" s="25" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1" s="21">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>Introduction to Level 3 and its work plan</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="40" t="n"/>
+      <c r="G28" s="40" t="n"/>
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="25" t="n"/>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="25" t="n"/>
+      <c r="L28" s="25" t="n"/>
+      <c r="M28" s="25" t="n"/>
+      <c r="N28" s="25" t="n"/>
+      <c r="O28" s="25" t="n"/>
+      <c r="P28" s="25" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1" s="21">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>The emitter follower and its special circuits</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E29" s="28" t="n"/>
+      <c r="F29" s="40" t="n"/>
+      <c r="G29" s="40" t="n"/>
+      <c r="H29" s="25" t="n"/>
+      <c r="I29" s="25" t="n"/>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="25" t="n"/>
+      <c r="L29" s="25" t="n"/>
+      <c r="M29" s="25" t="n"/>
+      <c r="N29" s="25" t="n"/>
+      <c r="O29" s="25" t="n"/>
+      <c r="P29" s="25" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1" s="21">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>Designs for a conventional power supply with current limiters</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E30" s="28" t="n"/>
+      <c r="F30" s="40" t="n"/>
+      <c r="G30" s="40" t="n"/>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="25" t="n"/>
+      <c r="L30" s="25" t="n"/>
+      <c r="M30" s="25" t="n"/>
+      <c r="N30" s="25" t="n"/>
+      <c r="O30" s="25" t="n"/>
+      <c r="P30" s="25" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1" s="21">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>Unusual uses of the transistor</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E31" s="28" t="n"/>
+      <c r="F31" s="40" t="n"/>
+      <c r="G31" s="40" t="n"/>
+      <c r="H31" s="25" t="n"/>
+      <c r="I31" s="25" t="n"/>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="25" t="n"/>
+      <c r="L31" s="25" t="n"/>
+      <c r="M31" s="25" t="n"/>
+      <c r="N31" s="25" t="n"/>
+      <c r="O31" s="25" t="n"/>
+      <c r="P31" s="25" t="n"/>
+    </row>
+    <row r="32" ht="30" customHeight="1" s="21">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" s="25" t="inlineStr">
+        <is>
+          <t>Window (range) circuits and designing heater and temperature control circuits</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="40" t="n"/>
+      <c r="G32" s="40" t="n"/>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="25" t="n"/>
+      <c r="L32" s="25" t="n"/>
+      <c r="M32" s="25" t="n"/>
+      <c r="N32" s="25" t="n"/>
+      <c r="O32" s="25" t="n"/>
+      <c r="P32" s="25" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1" s="21">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>Short pulse generator: why?</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="40" t="n"/>
+      <c r="G33" s="40" t="n"/>
+      <c r="H33" s="25" t="n"/>
+      <c r="I33" s="25" t="n"/>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="25" t="n"/>
+      <c r="L33" s="25" t="n"/>
+      <c r="M33" s="25" t="n"/>
+      <c r="N33" s="25" t="n"/>
+      <c r="O33" s="25" t="n"/>
+      <c r="P33" s="25" t="n"/>
+    </row>
+    <row r="34" ht="30" customHeight="1" s="21">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" s="25" t="inlineStr">
+        <is>
+          <t>Running on a constant current (constant current source)</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E34" s="28" t="n"/>
+      <c r="F34" s="40" t="n"/>
+      <c r="G34" s="40" t="n"/>
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="25" t="n"/>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="25" t="n"/>
+      <c r="L34" s="25" t="n"/>
+      <c r="M34" s="25" t="n"/>
+      <c r="N34" s="25" t="n"/>
+      <c r="O34" s="25" t="n"/>
+      <c r="P34" s="25" t="n"/>
+    </row>
+    <row r="35" ht="30" customHeight="1" s="21">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" s="25" t="inlineStr">
+        <is>
+          <t>Designing current mirrors and circuits without resistors</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E35" s="28" t="n"/>
+      <c r="F35" s="40" t="n"/>
+      <c r="G35" s="40" t="n"/>
+      <c r="H35" s="25" t="n"/>
+      <c r="I35" s="25" t="n"/>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="25" t="n"/>
+      <c r="L35" s="25" t="n"/>
+      <c r="M35" s="25" t="n"/>
+      <c r="N35" s="25" t="n"/>
+      <c r="O35" s="25" t="n"/>
+      <c r="P35" s="25" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1" s="21">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" s="25" t="inlineStr">
+        <is>
+          <t>The differential amplifier and why it is so popular</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E36" s="28" t="n"/>
+      <c r="F36" s="40" t="n"/>
+      <c r="G36" s="40" t="n"/>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="25" t="n"/>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="25" t="n"/>
+      <c r="L36" s="25" t="n"/>
+      <c r="M36" s="25" t="n"/>
+      <c r="N36" s="25" t="n"/>
+      <c r="O36" s="25" t="n"/>
+      <c r="P36" s="25" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1" s="21">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>Advanced amplifier topics (bootstrap, Miller effect, cascode)</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E37" s="28" t="n"/>
+      <c r="F37" s="40" t="n"/>
+      <c r="G37" s="40" t="n"/>
+      <c r="H37" s="25" t="n"/>
+      <c r="I37" s="25" t="n"/>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="25" t="n"/>
+      <c r="L37" s="25" t="n"/>
+      <c r="M37" s="25" t="n"/>
+      <c r="N37" s="25" t="n"/>
+      <c r="O37" s="25" t="n"/>
+      <c r="P37" s="25" t="n"/>
+    </row>
+    <row r="38" ht="30" customHeight="1" s="21">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" s="25" t="inlineStr">
+        <is>
+          <t>Oscillators (Hartley, Colpitts, crystal) with a practical experiment</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="40" t="n"/>
+      <c r="G38" s="40" t="n"/>
+      <c r="H38" s="25" t="n"/>
+      <c r="I38" s="25" t="n"/>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="25" t="n"/>
+      <c r="L38" s="25" t="n"/>
+      <c r="M38" s="25" t="n"/>
+      <c r="N38" s="25" t="n"/>
+      <c r="O38" s="25" t="n"/>
+      <c r="P38" s="25" t="n"/>
+    </row>
+    <row r="39" ht="30" customHeight="1" s="21">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" s="25" t="inlineStr">
+        <is>
+          <t>Sending a wireless signal remotely (the simplest circuit)</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="40" t="n"/>
+      <c r="G39" s="40" t="n"/>
+      <c r="H39" s="25" t="n"/>
+      <c r="I39" s="25" t="n"/>
+      <c r="J39" s="25" t="n"/>
+      <c r="K39" s="25" t="n"/>
+      <c r="L39" s="25" t="n"/>
+      <c r="M39" s="25" t="n"/>
+      <c r="N39" s="25" t="n"/>
+      <c r="O39" s="25" t="n"/>
+      <c r="P39" s="25" t="n"/>
+    </row>
+    <row r="40" ht="30" customHeight="1" s="21">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" s="25" t="inlineStr">
+        <is>
+          <t>What's inside the 555 timer</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="40" t="n"/>
+      <c r="G40" s="40" t="n"/>
+      <c r="H40" s="25" t="n"/>
+      <c r="I40" s="25" t="n"/>
+      <c r="J40" s="25" t="n"/>
+      <c r="K40" s="25" t="n"/>
+      <c r="L40" s="25" t="n"/>
+      <c r="M40" s="25" t="n"/>
+      <c r="N40" s="25" t="n"/>
+      <c r="O40" s="25" t="n"/>
+      <c r="P40" s="25" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1" s="21">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="n">
+        <v>39</v>
+      </c>
+      <c r="C41" s="25" t="inlineStr">
+        <is>
+          <t>A broader understanding of the 555 timer, with an interactive circuit design</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E41" s="28" t="n"/>
+      <c r="F41" s="40" t="n"/>
+      <c r="G41" s="40" t="n"/>
+      <c r="H41" s="25" t="n"/>
+      <c r="I41" s="25" t="n"/>
+      <c r="J41" s="25" t="n"/>
+      <c r="K41" s="25" t="n"/>
+      <c r="L41" s="25" t="n"/>
+      <c r="M41" s="25" t="n"/>
+      <c r="N41" s="25" t="n"/>
+      <c r="O41" s="25" t="n"/>
+      <c r="P41" s="25" t="n"/>
+    </row>
+    <row r="42" ht="30" customHeight="1" s="21">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B42" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="C42" s="25" t="inlineStr">
+        <is>
+          <t>Marketable 555 timer applications</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="40" t="n"/>
+      <c r="G42" s="40" t="n"/>
+      <c r="H42" s="25" t="n"/>
+      <c r="I42" s="25" t="n"/>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="25" t="n"/>
+      <c r="L42" s="25" t="n"/>
+      <c r="M42" s="25" t="n"/>
+      <c r="N42" s="25" t="n"/>
+      <c r="O42" s="25" t="n"/>
+      <c r="P42" s="25" t="n"/>
+    </row>
+    <row r="43" ht="30" customHeight="1" s="21">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="n">
+        <v>41</v>
+      </c>
+      <c r="C43" s="25" t="inlineStr">
+        <is>
+          <t>Designing a sequential-function circuit for a factory with the 555</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="40" t="n"/>
+      <c r="G43" s="40" t="n"/>
+      <c r="H43" s="25" t="n"/>
+      <c r="I43" s="25" t="n"/>
+      <c r="J43" s="25" t="n"/>
+      <c r="K43" s="25" t="n"/>
+      <c r="L43" s="25" t="n"/>
+      <c r="M43" s="25" t="n"/>
+      <c r="N43" s="25" t="n"/>
+      <c r="O43" s="25" t="n"/>
+      <c r="P43" s="25" t="n"/>
+    </row>
+    <row r="44" ht="30" customHeight="1" s="21">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B44" s="26" t="n">
+        <v>42</v>
+      </c>
+      <c r="C44" s="25" t="inlineStr">
+        <is>
+          <t>Designing a driver-assist circuit for a car factory</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="40" t="n"/>
+      <c r="G44" s="40" t="n"/>
+      <c r="H44" s="25" t="n"/>
+      <c r="I44" s="25" t="n"/>
+      <c r="J44" s="25" t="n"/>
+      <c r="K44" s="25" t="n"/>
+      <c r="L44" s="25" t="n"/>
+      <c r="M44" s="25" t="n"/>
+      <c r="N44" s="25" t="n"/>
+      <c r="O44" s="25" t="n"/>
+      <c r="P44" s="25" t="n"/>
+    </row>
+    <row r="45" ht="30" customHeight="1" s="21">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="C45" s="25" t="inlineStr">
+        <is>
+          <t>How to make use of the CD4017</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E45" s="28" t="n"/>
+      <c r="F45" s="40" t="n"/>
+      <c r="G45" s="40" t="n"/>
+      <c r="H45" s="25" t="n"/>
+      <c r="I45" s="25" t="n"/>
+      <c r="J45" s="25" t="n"/>
+      <c r="K45" s="25" t="n"/>
+      <c r="L45" s="25" t="n"/>
+      <c r="M45" s="25" t="n"/>
+      <c r="N45" s="25" t="n"/>
+      <c r="O45" s="25" t="n"/>
+      <c r="P45" s="25" t="n"/>
+    </row>
+    <row r="46" ht="30" customHeight="1" s="21">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B46" s="26" t="n">
+        <v>44</v>
+      </c>
+      <c r="C46" s="25" t="inlineStr">
+        <is>
+          <t>Designing a multi-timer circuit that splits time between different tasks</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E46" s="28" t="n"/>
+      <c r="F46" s="40" t="n"/>
+      <c r="G46" s="40" t="n"/>
+      <c r="H46" s="25" t="n"/>
+      <c r="I46" s="25" t="n"/>
+      <c r="J46" s="25" t="n"/>
+      <c r="K46" s="25" t="n"/>
+      <c r="L46" s="25" t="n"/>
+      <c r="M46" s="25" t="n"/>
+      <c r="N46" s="25" t="n"/>
+      <c r="O46" s="25" t="n"/>
+      <c r="P46" s="25" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1" s="21">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="C47" s="25" t="inlineStr">
+        <is>
+          <t>The queen of sequential events, and designing a circuit for a food factory</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="40" t="n"/>
+      <c r="G47" s="40" t="n"/>
+      <c r="H47" s="25" t="n"/>
+      <c r="I47" s="25" t="n"/>
+      <c r="J47" s="25" t="n"/>
+      <c r="K47" s="25" t="n"/>
+      <c r="L47" s="25" t="n"/>
+      <c r="M47" s="25" t="n"/>
+      <c r="N47" s="25" t="n"/>
+      <c r="O47" s="25" t="n"/>
+      <c r="P47" s="25" t="n"/>
+    </row>
+    <row r="48" ht="30" customHeight="1" s="21">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B48" s="26" t="n">
+        <v>46</v>
+      </c>
+      <c r="C48" s="25" t="inlineStr">
+        <is>
+          <t>Designing an efficient traffic light circuit without programming</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="40" t="n"/>
+      <c r="G48" s="40" t="n"/>
+      <c r="H48" s="25" t="n"/>
+      <c r="I48" s="25" t="n"/>
+      <c r="J48" s="25" t="n"/>
+      <c r="K48" s="25" t="n"/>
+      <c r="L48" s="25" t="n"/>
+      <c r="M48" s="25" t="n"/>
+      <c r="N48" s="25" t="n"/>
+      <c r="O48" s="25" t="n"/>
+      <c r="P48" s="25" t="n"/>
+    </row>
+    <row r="49" ht="30" customHeight="1" s="21">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B49" s="26" t="n">
+        <v>47</v>
+      </c>
+      <c r="C49" s="25" t="inlineStr">
+        <is>
+          <t>Designing an interactive clap switch to turn a device on and off</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E49" s="28" t="n"/>
+      <c r="F49" s="40" t="n"/>
+      <c r="G49" s="40" t="n"/>
+      <c r="H49" s="25" t="n"/>
+      <c r="I49" s="25" t="n"/>
+      <c r="J49" s="25" t="n"/>
+      <c r="K49" s="25" t="n"/>
+      <c r="L49" s="25" t="n"/>
+      <c r="M49" s="25" t="n"/>
+      <c r="N49" s="25" t="n"/>
+      <c r="O49" s="25" t="n"/>
+      <c r="P49" s="25" t="n"/>
+    </row>
+    <row r="50" ht="30" customHeight="1" s="21">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B50" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="C50" s="25" t="inlineStr">
+        <is>
+          <t>Designing an interactive circuit to control light brightness with a single switch</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E50" s="28" t="n"/>
+      <c r="F50" s="40" t="n"/>
+      <c r="G50" s="40" t="n"/>
+      <c r="H50" s="25" t="n"/>
+      <c r="I50" s="25" t="n"/>
+      <c r="J50" s="25" t="n"/>
+      <c r="K50" s="25" t="n"/>
+      <c r="L50" s="25" t="n"/>
+      <c r="M50" s="25" t="n"/>
+      <c r="N50" s="25" t="n"/>
+      <c r="O50" s="25" t="n"/>
+      <c r="P50" s="25" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1" s="21">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B51" s="26" t="n">
+        <v>49</v>
+      </c>
+      <c r="C51" s="25" t="inlineStr">
+        <is>
+          <t>Designing a simple electronic lock circuit without programming</t>
+        </is>
+      </c>
+      <c r="D51" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="40" t="n"/>
+      <c r="G51" s="40" t="n"/>
+      <c r="H51" s="25" t="n"/>
+      <c r="I51" s="25" t="n"/>
+      <c r="J51" s="25" t="n"/>
+      <c r="K51" s="25" t="n"/>
+      <c r="L51" s="25" t="n"/>
+      <c r="M51" s="25" t="n"/>
+      <c r="N51" s="25" t="n"/>
+      <c r="O51" s="25" t="n"/>
+      <c r="P51" s="25" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1" s="21">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B52" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="C52" s="25" t="inlineStr">
+        <is>
+          <t>Designing a circuit to control several devices remotely</t>
+        </is>
+      </c>
+      <c r="D52" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E52" s="28" t="n"/>
+      <c r="F52" s="40" t="n"/>
+      <c r="G52" s="40" t="n"/>
+      <c r="H52" s="25" t="n"/>
+      <c r="I52" s="25" t="n"/>
+      <c r="J52" s="25" t="n"/>
+      <c r="K52" s="25" t="n"/>
+      <c r="L52" s="25" t="n"/>
+      <c r="M52" s="25" t="n"/>
+      <c r="N52" s="25" t="n"/>
+      <c r="O52" s="25" t="n"/>
+      <c r="P52" s="25" t="n"/>
+    </row>
+    <row r="53" ht="30" customHeight="1" s="21">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B53" s="26" t="n">
+        <v>51</v>
+      </c>
+      <c r="C53" s="25" t="inlineStr">
+        <is>
+          <t>Explaining various circuits that use the simplest components for many tasks</t>
+        </is>
+      </c>
+      <c r="D53" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E53" s="28" t="n"/>
+      <c r="F53" s="40" t="n"/>
+      <c r="G53" s="40" t="n"/>
+      <c r="H53" s="25" t="n"/>
+      <c r="I53" s="25" t="n"/>
+      <c r="J53" s="25" t="n"/>
+      <c r="K53" s="25" t="n"/>
+      <c r="L53" s="25" t="n"/>
+      <c r="M53" s="25" t="n"/>
+      <c r="N53" s="25" t="n"/>
+      <c r="O53" s="25" t="n"/>
+      <c r="P53" s="25" t="n"/>
+    </row>
+    <row r="54" ht="30" customHeight="1" s="21">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B54" s="26" t="n">
+        <v>52</v>
+      </c>
+      <c r="C54" s="25" t="inlineStr">
+        <is>
+          <t>Introduction to Level 5: the purpose of these circuits and block-diagram design</t>
+        </is>
+      </c>
+      <c r="D54" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E54" s="28" t="n"/>
+      <c r="F54" s="40" t="n"/>
+      <c r="G54" s="40" t="n"/>
+      <c r="H54" s="25" t="n"/>
+      <c r="I54" s="25" t="n"/>
+      <c r="J54" s="25" t="n"/>
+      <c r="K54" s="25" t="n"/>
+      <c r="L54" s="25" t="n"/>
+      <c r="M54" s="25" t="n"/>
+      <c r="N54" s="25" t="n"/>
+      <c r="O54" s="25" t="n"/>
+      <c r="P54" s="25" t="n"/>
+    </row>
+    <row r="55" ht="30" customHeight="1" s="21">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B55" s="26" t="n">
+        <v>53</v>
+      </c>
+      <c r="C55" s="25" t="inlineStr">
+        <is>
+          <t>Information sources used by professionals, and getting schematics</t>
+        </is>
+      </c>
+      <c r="D55" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E55" s="28" t="n"/>
+      <c r="F55" s="40" t="n"/>
+      <c r="G55" s="40" t="n"/>
+      <c r="H55" s="25" t="n"/>
+      <c r="I55" s="25" t="n"/>
+      <c r="J55" s="25" t="n"/>
+      <c r="K55" s="25" t="n"/>
+      <c r="L55" s="25" t="n"/>
+      <c r="M55" s="25" t="n"/>
+      <c r="N55" s="25" t="n"/>
+      <c r="O55" s="25" t="n"/>
+      <c r="P55" s="25" t="n"/>
+    </row>
+    <row r="56" ht="30" customHeight="1" s="21">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B56" s="26" t="n">
+        <v>54</v>
+      </c>
+      <c r="C56" s="25" t="inlineStr">
+        <is>
+          <t>Information sources and how to choose ICs for specific functions</t>
+        </is>
+      </c>
+      <c r="D56" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E56" s="28" t="n"/>
+      <c r="F56" s="40" t="n"/>
+      <c r="G56" s="40" t="n"/>
+      <c r="H56" s="25" t="n"/>
+      <c r="I56" s="25" t="n"/>
+      <c r="J56" s="25" t="n"/>
+      <c r="K56" s="25" t="n"/>
+      <c r="L56" s="25" t="n"/>
+      <c r="M56" s="25" t="n"/>
+      <c r="N56" s="25" t="n"/>
+      <c r="O56" s="25" t="n"/>
+      <c r="P56" s="25" t="n"/>
+    </row>
+    <row r="57" ht="30" customHeight="1" s="21">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B57" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="C57" s="25" t="inlineStr">
+        <is>
+          <t>Information from other varied sources</t>
+        </is>
+      </c>
+      <c r="D57" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E57" s="28" t="n"/>
+      <c r="F57" s="40" t="n"/>
+      <c r="G57" s="40" t="n"/>
+      <c r="H57" s="25" t="n"/>
+      <c r="I57" s="25" t="n"/>
+      <c r="J57" s="25" t="n"/>
+      <c r="K57" s="25" t="n"/>
+      <c r="L57" s="25" t="n"/>
+      <c r="M57" s="25" t="n"/>
+      <c r="N57" s="25" t="n"/>
+      <c r="O57" s="25" t="n"/>
+      <c r="P57" s="25" t="n"/>
+    </row>
+    <row r="58" ht="30" customHeight="1" s="21">
+      <c r="A58" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B58" s="26" t="n">
+        <v>56</v>
+      </c>
+      <c r="C58" s="25" t="inlineStr">
+        <is>
+          <t>Designing a lithium battery charger circuit with dedicated ICs</t>
+        </is>
+      </c>
+      <c r="D58" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E58" s="28" t="n"/>
+      <c r="F58" s="40" t="n"/>
+      <c r="G58" s="40" t="n"/>
+      <c r="H58" s="25" t="n"/>
+      <c r="I58" s="25" t="n"/>
+      <c r="J58" s="25" t="n"/>
+      <c r="K58" s="25" t="n"/>
+      <c r="L58" s="25" t="n"/>
+      <c r="M58" s="25" t="n"/>
+      <c r="N58" s="25" t="n"/>
+      <c r="O58" s="25" t="n"/>
+      <c r="P58" s="25" t="n"/>
+    </row>
+    <row r="59" ht="30" customHeight="1" s="21">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B59" s="26" t="n">
+        <v>57</v>
+      </c>
+      <c r="C59" s="25" t="inlineStr">
+        <is>
+          <t>Developing a professional, competitive high-voltage probe</t>
+        </is>
+      </c>
+      <c r="D59" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E59" s="28" t="n"/>
+      <c r="F59" s="40" t="n"/>
+      <c r="G59" s="40" t="n"/>
+      <c r="H59" s="25" t="n"/>
+      <c r="I59" s="25" t="n"/>
+      <c r="J59" s="25" t="n"/>
+      <c r="K59" s="25" t="n"/>
+      <c r="L59" s="25" t="n"/>
+      <c r="M59" s="25" t="n"/>
+      <c r="N59" s="25" t="n"/>
+      <c r="O59" s="25" t="n"/>
+      <c r="P59" s="25" t="n"/>
+    </row>
+    <row r="60" ht="30" customHeight="1" s="21">
+      <c r="A60" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B60" s="26" t="n">
+        <v>58</v>
+      </c>
+      <c r="C60" s="25" t="inlineStr">
+        <is>
+          <t>Developing a cheap, competitive light-intensity sensor</t>
+        </is>
+      </c>
+      <c r="D60" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E60" s="28" t="n"/>
+      <c r="F60" s="40" t="n"/>
+      <c r="G60" s="40" t="n"/>
+      <c r="H60" s="25" t="n"/>
+      <c r="I60" s="25" t="n"/>
+      <c r="J60" s="25" t="n"/>
+      <c r="K60" s="25" t="n"/>
+      <c r="L60" s="25" t="n"/>
+      <c r="M60" s="25" t="n"/>
+      <c r="N60" s="25" t="n"/>
+      <c r="O60" s="25" t="n"/>
+      <c r="P60" s="25" t="n"/>
+    </row>
+    <row r="61" ht="30" customHeight="1" s="21">
+      <c r="A61" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B61" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="C61" s="25" t="inlineStr">
+        <is>
+          <t>Analysing a market circuit: induction heating</t>
+        </is>
+      </c>
+      <c r="D61" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E61" s="28" t="n"/>
+      <c r="F61" s="40" t="n"/>
+      <c r="G61" s="40" t="n"/>
+      <c r="H61" s="25" t="n"/>
+      <c r="I61" s="25" t="n"/>
+      <c r="J61" s="25" t="n"/>
+      <c r="K61" s="25" t="n"/>
+      <c r="L61" s="25" t="n"/>
+      <c r="M61" s="25" t="n"/>
+      <c r="N61" s="25" t="n"/>
+      <c r="O61" s="25" t="n"/>
+      <c r="P61" s="25" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1" s="21">
+      <c r="A62" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B62" s="26" t="n">
+        <v>60</v>
+      </c>
+      <c r="C62" s="25" t="inlineStr">
+        <is>
+          <t>Analysing a market circuit: high-frequency inverter</t>
+        </is>
+      </c>
+      <c r="D62" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E62" s="28" t="n"/>
+      <c r="F62" s="40" t="n"/>
+      <c r="G62" s="40" t="n"/>
+      <c r="H62" s="25" t="n"/>
+      <c r="I62" s="25" t="n"/>
+      <c r="J62" s="25" t="n"/>
+      <c r="K62" s="25" t="n"/>
+      <c r="L62" s="25" t="n"/>
+      <c r="M62" s="25" t="n"/>
+      <c r="N62" s="25" t="n"/>
+      <c r="O62" s="25" t="n"/>
+      <c r="P62" s="25" t="n"/>
+    </row>
+    <row r="63" ht="30" customHeight="1" s="21">
+      <c r="A63" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B63" s="26" t="n">
+        <v>61</v>
+      </c>
+      <c r="C63" s="25" t="inlineStr">
+        <is>
+          <t>Analysing a market circuit: car inverter from the cigarette-lighter socket</t>
+        </is>
+      </c>
+      <c r="D63" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E63" s="28" t="n"/>
+      <c r="F63" s="40" t="n"/>
+      <c r="G63" s="40" t="n"/>
+      <c r="H63" s="25" t="n"/>
+      <c r="I63" s="25" t="n"/>
+      <c r="J63" s="25" t="n"/>
+      <c r="K63" s="25" t="n"/>
+      <c r="L63" s="25" t="n"/>
+      <c r="M63" s="25" t="n"/>
+      <c r="N63" s="25" t="n"/>
+      <c r="O63" s="25" t="n"/>
+      <c r="P63" s="25" t="n"/>
+    </row>
+    <row r="64" ht="30" customHeight="1" s="21">
+      <c r="A64" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B64" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="C64" s="25" t="inlineStr">
+        <is>
+          <t>Types of power converters</t>
+        </is>
+      </c>
+      <c r="D64" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E64" s="28" t="n"/>
+      <c r="F64" s="40" t="n"/>
+      <c r="G64" s="40" t="n"/>
+      <c r="H64" s="25" t="n"/>
+      <c r="I64" s="25" t="n"/>
+      <c r="J64" s="25" t="n"/>
+      <c r="K64" s="25" t="n"/>
+      <c r="L64" s="25" t="n"/>
+      <c r="M64" s="25" t="n"/>
+      <c r="N64" s="25" t="n"/>
+      <c r="O64" s="25" t="n"/>
+      <c r="P64" s="25" t="n"/>
+    </row>
+    <row r="65" ht="30" customHeight="1" s="21">
+      <c r="A65" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B65" s="26" t="n">
+        <v>63</v>
+      </c>
+      <c r="C65" s="25" t="inlineStr">
+        <is>
+          <t>How the power inverter works</t>
+        </is>
+      </c>
+      <c r="D65" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E65" s="28" t="n"/>
+      <c r="F65" s="40" t="n"/>
+      <c r="G65" s="40" t="n"/>
+      <c r="H65" s="25" t="n"/>
+      <c r="I65" s="25" t="n"/>
+      <c r="J65" s="25" t="n"/>
+      <c r="K65" s="25" t="n"/>
+      <c r="L65" s="25" t="n"/>
+      <c r="M65" s="25" t="n"/>
+      <c r="N65" s="25" t="n"/>
+      <c r="O65" s="25" t="n"/>
+      <c r="P65" s="25" t="n"/>
+    </row>
+    <row r="66" ht="30" customHeight="1" s="21">
+      <c r="A66" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B66" s="26" t="n">
+        <v>64</v>
+      </c>
+      <c r="C66" s="25" t="inlineStr">
+        <is>
+          <t>What is SPWM?</t>
+        </is>
+      </c>
+      <c r="D66" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E66" s="28" t="n"/>
+      <c r="F66" s="40" t="n"/>
+      <c r="G66" s="40" t="n"/>
+      <c r="H66" s="25" t="n"/>
+      <c r="I66" s="25" t="n"/>
+      <c r="J66" s="25" t="n"/>
+      <c r="K66" s="25" t="n"/>
+      <c r="L66" s="25" t="n"/>
+      <c r="M66" s="25" t="n"/>
+      <c r="N66" s="25" t="n"/>
+      <c r="O66" s="25" t="n"/>
+      <c r="P66" s="25" t="n"/>
+    </row>
+    <row r="67" ht="30" customHeight="1" s="21">
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B67" s="26" t="n">
+        <v>65</v>
+      </c>
+      <c r="C67" s="25" t="inlineStr">
+        <is>
+          <t>Developing a new frequency-detection circuit</t>
+        </is>
+      </c>
+      <c r="D67" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E67" s="28" t="n"/>
+      <c r="F67" s="40" t="n"/>
+      <c r="G67" s="40" t="n"/>
+      <c r="H67" s="25" t="n"/>
+      <c r="I67" s="25" t="n"/>
+      <c r="J67" s="25" t="n"/>
+      <c r="K67" s="25" t="n"/>
+      <c r="L67" s="25" t="n"/>
+      <c r="M67" s="25" t="n"/>
+      <c r="N67" s="25" t="n"/>
+      <c r="O67" s="25" t="n"/>
+      <c r="P67" s="25" t="n"/>
+    </row>
+    <row r="68" ht="30" customHeight="1" s="21">
+      <c r="A68" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B68" s="26" t="n">
+        <v>66</v>
+      </c>
+      <c r="C68" s="25" t="inlineStr">
+        <is>
+          <t>Developing a new market circuit for temperature control with aluminium heat sinking</t>
+        </is>
+      </c>
+      <c r="D68" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E68" s="28" t="n"/>
+      <c r="F68" s="40" t="n"/>
+      <c r="G68" s="40" t="n"/>
+      <c r="H68" s="25" t="n"/>
+      <c r="I68" s="25" t="n"/>
+      <c r="J68" s="25" t="n"/>
+      <c r="K68" s="25" t="n"/>
+      <c r="L68" s="25" t="n"/>
+      <c r="M68" s="25" t="n"/>
+      <c r="N68" s="25" t="n"/>
+      <c r="O68" s="25" t="n"/>
+      <c r="P68" s="25" t="n"/>
+    </row>
+    <row r="69" ht="30" customHeight="1" s="21">
+      <c r="A69" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B69" s="26" t="n">
+        <v>67</v>
+      </c>
+      <c r="C69" s="25" t="inlineStr">
+        <is>
+          <t>Introduction to the PCB course: what printed circuit boards are</t>
+        </is>
+      </c>
+      <c r="D69" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E69" s="28" t="n"/>
+      <c r="F69" s="40" t="n"/>
+      <c r="G69" s="40" t="n"/>
+      <c r="H69" s="25" t="n"/>
+      <c r="I69" s="25" t="n"/>
+      <c r="J69" s="25" t="n"/>
+      <c r="K69" s="25" t="n"/>
+      <c r="L69" s="25" t="n"/>
+      <c r="M69" s="25" t="n"/>
+      <c r="N69" s="25" t="n"/>
+      <c r="O69" s="25" t="n"/>
+      <c r="P69" s="25" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1" s="21">
+      <c r="A70" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B70" s="26" t="n">
+        <v>68</v>
+      </c>
+      <c r="C70" s="25" t="inlineStr">
+        <is>
+          <t>Various practical examples of distinctive PCBs</t>
+        </is>
+      </c>
+      <c r="D70" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E70" s="28" t="n"/>
+      <c r="F70" s="40" t="n"/>
+      <c r="G70" s="40" t="n"/>
+      <c r="H70" s="25" t="n"/>
+      <c r="I70" s="25" t="n"/>
+      <c r="J70" s="25" t="n"/>
+      <c r="K70" s="25" t="n"/>
+      <c r="L70" s="25" t="n"/>
+      <c r="M70" s="25" t="n"/>
+      <c r="N70" s="25" t="n"/>
+      <c r="O70" s="25" t="n"/>
+      <c r="P70" s="25" t="n"/>
+    </row>
+    <row r="71" ht="30" customHeight="1" s="21">
+      <c r="A71" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B71" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="C71" s="25" t="inlineStr">
+        <is>
+          <t>PCB manufacturing processes by different methods, plus soldering</t>
+        </is>
+      </c>
+      <c r="D71" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E71" s="28" t="n"/>
+      <c r="F71" s="40" t="n"/>
+      <c r="G71" s="40" t="n"/>
+      <c r="H71" s="25" t="n"/>
+      <c r="I71" s="25" t="n"/>
+      <c r="J71" s="25" t="n"/>
+      <c r="K71" s="25" t="n"/>
+      <c r="L71" s="25" t="n"/>
+      <c r="M71" s="25" t="n"/>
+      <c r="N71" s="25" t="n"/>
+      <c r="O71" s="25" t="n"/>
+      <c r="P71" s="25" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1" s="21">
+      <c r="A72" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B72" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="C72" s="25" t="inlineStr">
+        <is>
+          <t>Designing the first PCB and an introduction to EasyEDA</t>
+        </is>
+      </c>
+      <c r="D72" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E72" s="28" t="n"/>
+      <c r="F72" s="40" t="n"/>
+      <c r="G72" s="40" t="n"/>
+      <c r="H72" s="25" t="n"/>
+      <c r="I72" s="25" t="n"/>
+      <c r="J72" s="25" t="n"/>
+      <c r="K72" s="25" t="n"/>
+      <c r="L72" s="25" t="n"/>
+      <c r="M72" s="25" t="n"/>
+      <c r="N72" s="25" t="n"/>
+      <c r="O72" s="25" t="n"/>
+      <c r="P72" s="25" t="n"/>
+    </row>
+    <row r="73" ht="30" customHeight="1" s="21">
+      <c r="A73" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B73" s="26" t="n">
+        <v>71</v>
+      </c>
+      <c r="C73" s="25" t="inlineStr">
+        <is>
+          <t>Designing a PCB for a sound detector circuit</t>
+        </is>
+      </c>
+      <c r="D73" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E73" s="28" t="n"/>
+      <c r="F73" s="40" t="n"/>
+      <c r="G73" s="40" t="n"/>
+      <c r="H73" s="25" t="n"/>
+      <c r="I73" s="25" t="n"/>
+      <c r="J73" s="25" t="n"/>
+      <c r="K73" s="25" t="n"/>
+      <c r="L73" s="25" t="n"/>
+      <c r="M73" s="25" t="n"/>
+      <c r="N73" s="25" t="n"/>
+      <c r="O73" s="25" t="n"/>
+      <c r="P73" s="25" t="n"/>
+    </row>
+    <row r="74" ht="30" customHeight="1" s="21">
+      <c r="A74" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B74" s="26" t="n">
+        <v>72</v>
+      </c>
+      <c r="C74" s="25" t="inlineStr">
+        <is>
+          <t>What matters about isolation in PCBs</t>
+        </is>
+      </c>
+      <c r="D74" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E74" s="28" t="n"/>
+      <c r="F74" s="40" t="n"/>
+      <c r="G74" s="40" t="n"/>
+      <c r="H74" s="25" t="n"/>
+      <c r="I74" s="25" t="n"/>
+      <c r="J74" s="25" t="n"/>
+      <c r="K74" s="25" t="n"/>
+      <c r="L74" s="25" t="n"/>
+      <c r="M74" s="25" t="n"/>
+      <c r="N74" s="25" t="n"/>
+      <c r="O74" s="25" t="n"/>
+      <c r="P74" s="25" t="n"/>
+    </row>
+    <row r="75" ht="30" customHeight="1" s="21">
+      <c r="A75" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B75" s="26" t="n">
+        <v>73</v>
+      </c>
+      <c r="C75" s="25" t="inlineStr">
+        <is>
+          <t>What creepage means in PCB design and why it matters</t>
+        </is>
+      </c>
+      <c r="D75" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E75" s="28" t="n"/>
+      <c r="F75" s="40" t="n"/>
+      <c r="G75" s="40" t="n"/>
+      <c r="H75" s="25" t="n"/>
+      <c r="I75" s="25" t="n"/>
+      <c r="J75" s="25" t="n"/>
+      <c r="K75" s="25" t="n"/>
+      <c r="L75" s="25" t="n"/>
+      <c r="M75" s="25" t="n"/>
+      <c r="N75" s="25" t="n"/>
+      <c r="O75" s="25" t="n"/>
+      <c r="P75" s="25" t="n"/>
+    </row>
+    <row r="76" ht="30" customHeight="1" s="21">
+      <c r="A76" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B76" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="C76" s="25" t="inlineStr">
+        <is>
+          <t>SMD soldering and what a stencil is</t>
+        </is>
+      </c>
+      <c r="D76" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E76" s="28" t="n"/>
+      <c r="F76" s="40" t="n"/>
+      <c r="G76" s="40" t="n"/>
+      <c r="H76" s="25" t="n"/>
+      <c r="I76" s="25" t="n"/>
+      <c r="J76" s="25" t="n"/>
+      <c r="K76" s="25" t="n"/>
+      <c r="L76" s="25" t="n"/>
+      <c r="M76" s="25" t="n"/>
+      <c r="N76" s="25" t="n"/>
+      <c r="O76" s="25" t="n"/>
+      <c r="P76" s="25" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1" s="21">
+      <c r="A77" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B77" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="C77" s="25" t="inlineStr">
+        <is>
+          <t>Manufacturing a PCB on aluminium</t>
+        </is>
+      </c>
+      <c r="D77" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E77" s="28" t="n"/>
+      <c r="F77" s="40" t="n"/>
+      <c r="G77" s="40" t="n"/>
+      <c r="H77" s="25" t="n"/>
+      <c r="I77" s="25" t="n"/>
+      <c r="J77" s="25" t="n"/>
+      <c r="K77" s="25" t="n"/>
+      <c r="L77" s="25" t="n"/>
+      <c r="M77" s="25" t="n"/>
+      <c r="N77" s="25" t="n"/>
+      <c r="O77" s="25" t="n"/>
+      <c r="P77" s="25" t="n"/>
+    </row>
+    <row r="78" ht="30" customHeight="1" s="21">
+      <c r="A78" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B78" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="C78" s="25" t="inlineStr">
+        <is>
+          <t>Important considerations in PCB manufacturing for a more robust design</t>
+        </is>
+      </c>
+      <c r="D78" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E78" s="28" t="n"/>
+      <c r="F78" s="40" t="n"/>
+      <c r="G78" s="40" t="n"/>
+      <c r="H78" s="25" t="n"/>
+      <c r="I78" s="25" t="n"/>
+      <c r="J78" s="25" t="n"/>
+      <c r="K78" s="25" t="n"/>
+      <c r="L78" s="25" t="n"/>
+      <c r="M78" s="25" t="n"/>
+      <c r="N78" s="25" t="n"/>
+      <c r="O78" s="25" t="n"/>
+      <c r="P78" s="25" t="n"/>
+    </row>
+    <row r="79" ht="30" customHeight="1" s="21">
+      <c r="A79" s="25" t="inlineStr">
+        <is>
+          <t>Professional Electronic Design Course</t>
+        </is>
+      </c>
+      <c r="B79" s="26" t="n">
+        <v>77</v>
+      </c>
+      <c r="C79" s="25" t="inlineStr">
+        <is>
+          <t>How to benefit from electronic design experience, practically and financially</t>
+        </is>
+      </c>
+      <c r="D79" s="26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E79" s="28" t="n"/>
+      <c r="F79" s="40" t="n"/>
+      <c r="G79" s="40" t="n"/>
+      <c r="H79" s="25" t="n"/>
+      <c r="I79" s="25" t="n"/>
+      <c r="J79" s="25" t="n"/>
+      <c r="K79" s="25" t="n"/>
+      <c r="L79" s="25" t="n"/>
+      <c r="M79" s="25" t="n"/>
+      <c r="N79" s="25" t="n"/>
+      <c r="O79" s="25" t="n"/>
+      <c r="P79" s="25" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P40"/>
+  <autoFilter ref="A4:P200"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D5:D40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="D5:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Done,In progress,Not started"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" display="Open README" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" display="Watch video" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId6"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1651,7 +3361,7 @@
         </is>
       </c>
       <c r="B3" s="35">
-        <f>COUNTA(Episodes!B5:B40)</f>
+        <f>COUNTA(Episodes!B5:B200)</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +3372,7 @@
         </is>
       </c>
       <c r="B4" s="35">
-        <f>COUNTIF(Episodes!D5:D40,"Done")</f>
+        <f>COUNTIF(Episodes!D5:D200,"Done")</f>
         <v/>
       </c>
     </row>
@@ -1673,7 +3383,7 @@
         </is>
       </c>
       <c r="B5" s="35">
-        <f>COUNTIF(Episodes!D5:D40,"In progress")</f>
+        <f>COUNTIF(Episodes!D5:D200,"In progress")</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +3394,7 @@
         </is>
       </c>
       <c r="B6" s="35">
-        <f>COUNTIF(Episodes!D5:D40,"Not started")</f>
+        <f>COUNTIF(Episodes!D5:D200,"Not started")</f>
         <v/>
       </c>
     </row>
@@ -1706,10 +3416,11 @@
         </is>
       </c>
       <c r="B8" s="35">
-        <f>IF(B3=0,"-",MAX(Episodes!B5:B40))</f>
+        <f>IF(B3=0,"-",MAX(Episodes!B5:B200))</f>
         <v/>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="21">
       <c r="A10" s="37" t="inlineStr">
         <is>
@@ -1724,7 +3435,7 @@
         </is>
       </c>
       <c r="B11" s="34">
-        <f>COUNTIF(Episodes!A5:A40,A11)</f>
+        <f>COUNTIF(Episodes!A5:A200,A11)</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +3446,7 @@
         </is>
       </c>
       <c r="B12" s="34">
-        <f>COUNTIF(Episodes!A5:A40,A12)</f>
+        <f>COUNTIF(Episodes!A5:A200,A12)</f>
         <v/>
       </c>
     </row>
@@ -1746,7 +3457,7 @@
         </is>
       </c>
       <c r="B13" s="34">
-        <f>COUNTIF(Episodes!A5:A40,A13)</f>
+        <f>COUNTIF(Episodes!A5:A200,A13)</f>
         <v/>
       </c>
     </row>

--- a/Electricity-Diploma-Episode-Index.xlsx
+++ b/Electricity-Diploma-Episode-Index.xlsx
@@ -3420,7 +3420,6 @@
         <v/>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="21">
       <c r="A10" s="37" t="inlineStr">
         <is>
@@ -3493,7 +3492,7 @@
     <row r="3" ht="15" customHeight="1" s="21">
       <c r="A3" s="40" t="inlineStr">
         <is>
-          <t>• One row per episode on the Episodes sheet. Row 5 (ep08) is a filled example of the expected format.</t>
+          <t>• One row per episode on the Episodes sheet. Row 10 (ep08) is a filled example of the expected format.</t>
         </is>
       </c>
     </row>

--- a/Electricity-Diploma-Episode-Index.xlsx
+++ b/Electricity-Diploma-Episode-Index.xlsx
@@ -739,9 +739,9 @@
           <t>Designing a simple circuit (closed / open) with full calculations</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E5" s="28" t="n"/>
@@ -751,11 +751,23 @@
       <c r="I5" s="25" t="n"/>
       <c r="J5" s="25" t="n"/>
       <c r="K5" s="25" t="n"/>
-      <c r="L5" s="25" t="n"/>
+      <c r="L5" s="25" t="inlineStr">
+        <is>
+          <t>Done (files not uploaded yet)</t>
+        </is>
+      </c>
       <c r="M5" s="25" t="n"/>
-      <c r="N5" s="25" t="n"/>
+      <c r="N5" s="25" t="inlineStr">
+        <is>
+          <t>Not uploaded yet</t>
+        </is>
+      </c>
       <c r="O5" s="25" t="n"/>
-      <c r="P5" s="25" t="n"/>
+      <c r="P5" s="25" t="inlineStr">
+        <is>
+          <t>Finished with simulation. To do: add README summary + simulation files to GitHub.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="21">
       <c r="A6" s="25" t="inlineStr">
@@ -771,9 +783,9 @@
           <t>Designing a quiz board for two school teams</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E6" s="28" t="n"/>
@@ -783,11 +795,23 @@
       <c r="I6" s="25" t="n"/>
       <c r="J6" s="25" t="n"/>
       <c r="K6" s="25" t="n"/>
-      <c r="L6" s="25" t="n"/>
+      <c r="L6" s="25" t="inlineStr">
+        <is>
+          <t>Done (files not uploaded yet)</t>
+        </is>
+      </c>
       <c r="M6" s="25" t="n"/>
-      <c r="N6" s="25" t="n"/>
+      <c r="N6" s="25" t="inlineStr">
+        <is>
+          <t>Not uploaded yet</t>
+        </is>
+      </c>
       <c r="O6" s="25" t="n"/>
-      <c r="P6" s="25" t="n"/>
+      <c r="P6" s="25" t="inlineStr">
+        <is>
+          <t>Finished with simulation. To do: add README summary + simulation files to GitHub.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="21">
       <c r="A7" s="25" t="inlineStr">
@@ -803,9 +827,9 @@
           <t>Designing a large LED display board and choosing its component values</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E7" s="28" t="n"/>
@@ -815,11 +839,23 @@
       <c r="I7" s="25" t="n"/>
       <c r="J7" s="25" t="n"/>
       <c r="K7" s="25" t="n"/>
-      <c r="L7" s="25" t="n"/>
+      <c r="L7" s="25" t="inlineStr">
+        <is>
+          <t>Done (files not uploaded yet)</t>
+        </is>
+      </c>
       <c r="M7" s="25" t="n"/>
-      <c r="N7" s="25" t="n"/>
+      <c r="N7" s="25" t="inlineStr">
+        <is>
+          <t>Not uploaded yet</t>
+        </is>
+      </c>
       <c r="O7" s="25" t="n"/>
-      <c r="P7" s="25" t="n"/>
+      <c r="P7" s="25" t="inlineStr">
+        <is>
+          <t>Finished with simulation. To do: add README summary + simulation files to GitHub.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="21">
       <c r="A8" s="25" t="inlineStr">
@@ -835,9 +871,9 @@
           <t>Designing a relay circuit for a contest where the fastest team wins</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E8" s="28" t="n"/>
@@ -847,11 +883,23 @@
       <c r="I8" s="25" t="n"/>
       <c r="J8" s="25" t="n"/>
       <c r="K8" s="25" t="n"/>
-      <c r="L8" s="25" t="n"/>
+      <c r="L8" s="25" t="inlineStr">
+        <is>
+          <t>Done (files not uploaded yet)</t>
+        </is>
+      </c>
       <c r="M8" s="25" t="n"/>
-      <c r="N8" s="25" t="n"/>
+      <c r="N8" s="25" t="inlineStr">
+        <is>
+          <t>Not uploaded yet</t>
+        </is>
+      </c>
       <c r="O8" s="25" t="n"/>
-      <c r="P8" s="25" t="n"/>
+      <c r="P8" s="25" t="inlineStr">
+        <is>
+          <t>Finished with simulation. To do: add README summary + simulation files to GitHub.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1" s="21">
       <c r="A9" s="25" t="inlineStr">
@@ -867,9 +915,9 @@
           <t>Designing a fish tank circuit based on sunlight intensity, with a light cell</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E9" s="28" t="n"/>
@@ -879,11 +927,23 @@
       <c r="I9" s="25" t="n"/>
       <c r="J9" s="25" t="n"/>
       <c r="K9" s="25" t="n"/>
-      <c r="L9" s="25" t="n"/>
+      <c r="L9" s="25" t="inlineStr">
+        <is>
+          <t>Done (files not uploaded yet)</t>
+        </is>
+      </c>
       <c r="M9" s="25" t="n"/>
-      <c r="N9" s="25" t="n"/>
+      <c r="N9" s="25" t="inlineStr">
+        <is>
+          <t>Not uploaded yet</t>
+        </is>
+      </c>
       <c r="O9" s="25" t="n"/>
-      <c r="P9" s="25" t="n"/>
+      <c r="P9" s="25" t="inlineStr">
+        <is>
+          <t>Finished with simulation. To do: add README summary + simulation files to GitHub.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="165" customHeight="1" s="21">
       <c r="A10" s="25" t="inlineStr">

--- a/Electricity-Diploma-Episode-Index.xlsx
+++ b/Electricity-Diploma-Episode-Index.xlsx
@@ -1211,7 +1211,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="21">
+    <row r="13" ht="165" customHeight="1" s="21">
       <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Professional Electronic Design Course</t>
@@ -1225,23 +1225,80 @@
           <t>Designing a car-factory panel to control the cooling fan</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="n"/>
-      <c r="F13" s="40" t="n"/>
-      <c r="G13" s="40" t="n"/>
-      <c r="H13" s="25" t="n"/>
-      <c r="I13" s="25" t="n"/>
-      <c r="J13" s="25" t="n"/>
-      <c r="K13" s="25" t="n"/>
-      <c r="L13" s="25" t="n"/>
-      <c r="M13" s="25" t="n"/>
-      <c r="N13" s="25" t="n"/>
-      <c r="O13" s="25" t="n"/>
-      <c r="P13" s="25" t="n"/>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>Open README</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>Watch video</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>• Saturation: V_CE ≈ 0 → P = V_CE × I_C ≈ 0 → no heating
+• Car rule: every load grounded to the chassis, switch the positive (high) side
+• NPN above a grounded load = emitter follower, cannot saturate
+• Driver transistor: small NPN pulls a PNP base to 0 V so the PNP saturates
+• NTC thermistor in a voltage divider as a temperature switch</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
+        <is>
+          <t>1. Inverting pair with load below the NPN (fails to saturate: LED 7.8 V, motor 7 V)
+2. Driver transistor: BC547 NPN drives PNP high-side switch (+ indicator LED)
+3. Alternate form: PNP drives NPN (ground-active input)
+4. Car cooling fan controller: NTC thermistor divider → BC547B → BD140 → 12 V fan</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="inlineStr">
+        <is>
+          <t>P_loss = V_CE × I_C (2 V × 1.2 A ≈ 2.4 W)
+TIP31: 1 / 0.32 W/°C ≈ 3.1 °C/W
+V_out = V_in · R2 / (R1 + R2)
+0.4 = 12 · R2 / (8 kΩ + R2) → R2 ≈ 276 Ω → 100 Ω used</t>
+        </is>
+      </c>
+      <c r="K13" s="25" t="inlineStr">
+        <is>
+          <t>BD140 (PNP, high current), BC547B (NPN), NTC thermistor (≈ 8 kΩ at 25 °C, ≈ 100 Ω hot), R2 = 100 Ω, 1 kΩ, red LED, 12 V fan, 12 V supply. Datasheets read: TIP31/32 (40 W), BC547 (500 mW), 2N2222 (2.28 mW/°C)</t>
+        </is>
+      </c>
+      <c r="L13" s="25" t="inlineStr">
+        <is>
+          <t>Not done yet</t>
+        </is>
+      </c>
+      <c r="M13" s="25" t="inlineStr">
+        <is>
+          <t>Video sim: NPN above load → LED 7.8 V, motor ≈ 7–9 V (≈ 2 V lost); PNP driver → LED 11.58 V, lamp + motor ≈ 11 V, 11.18 V at 1.5 A with 1 kΩ. Fan sim: ≈ 0.5 V cold (off), ≈ 2 V hot (on).
+Hardware: soldering iron near thermistor → red LED + fan on; removed → off. Fan aimed at the sensor turns on/off quickly.</t>
+        </is>
+      </c>
+      <c r="N13" s="25" t="inlineStr">
+        <is>
+          <t>README only (no media yet)</t>
+        </is>
+      </c>
+      <c r="O13" s="25" t="inlineStr">
+        <is>
+          <t>A grounded load needs a PNP on the high side, and a small NPN driver is what pulls it fully into saturation. Add a thermistor divider in front and the same block becomes an automatic temperature-controlled fan.</t>
+        </is>
+      </c>
+      <c r="P13" s="25" t="inlineStr">
+        <is>
+          <t>To do: Circuit Wizard sim of the fan controller (sweep temperature, log divider and fan voltage); compare V_CE / power of NPN-above-load vs PNP driver at ≈ 1.2 A; find switch-on thermistor resistance (my estimate ≈ 2 kΩ).</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="21">
       <c r="A14" s="25" t="inlineStr">
@@ -3374,6 +3431,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId8"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Electricity-Diploma-Episode-Index.xlsx
+++ b/Electricity-Diploma-Episode-Index.xlsx
@@ -1227,7 +1227,7 @@
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E13" s="28" t="n">
@@ -1275,7 +1275,10 @@
       </c>
       <c r="L13" s="25" t="inlineStr">
         <is>
-          <t>Not done yet</t>
+          <t>• NPN above load: V_CE = 4.20 V (LED pull-up) / 4.12 V (10 kΩ pull-up) → load 7.8 V, matches video ✔
+• Driver BC547B → TIP127: LED V_CE = 412 mV ✔; motor V_CE = 489–577 mV ✔ (≈ 10× less waste)
+• PNP drives NPN, switch to ground: output NPN V_CE = 54.85 mV ✔
+• Fan controller (10 kΩ NTC, R5 = 100 Ω): off up to 56.9 °C; starts at 2.07 kΩ / 64.6 °C (my ≈ 2 kΩ estimate ✔); at 80 °C BD140 still drops 9.05 V ✘ (not saturated)</t>
         </is>
       </c>
       <c r="M13" s="25" t="inlineStr">
@@ -1286,17 +1289,17 @@
       </c>
       <c r="N13" s="25" t="inlineStr">
         <is>
-          <t>README only (no media yet)</t>
+          <t>6 simulation GIFs + MP4s: NPN above load (LED pull-up, 10 kΩ pull-up), TIP127 driver (LED, motor), PNP→NPN ground-active input, thermistor fan controller sweep</t>
         </is>
       </c>
       <c r="O13" s="25" t="inlineStr">
         <is>
-          <t>A grounded load needs a PNP on the high side, and a small NPN driver is what pulls it fully into saturation. Add a thermistor divider in front and the same block becomes an automatic temperature-controlled fan.</t>
+          <t>A grounded load needs a PNP on the high side, and a small NPN driver is what pulls it fully into saturation. Add a thermistor divider in front and the same block becomes an automatic temperature-controlled fan. In my sim, the fan controller showed that a driver only helps if the first transistor saturates too: a &lt; 1 V divider through 10 kΩ starves Q1, so the BD140 wasted ≈ 9 V.</t>
         </is>
       </c>
       <c r="P13" s="25" t="inlineStr">
         <is>
-          <t>To do: Circuit Wizard sim of the fan controller (sweep temperature, log divider and fan voltage); compare V_CE / power of NPN-above-load vs PNP driver at ≈ 1.2 A; find switch-on thermistor resistance (my estimate ≈ 2 kΩ).</t>
+          <t>Sims used TIP127 (PNP Darlington) instead of BD140 for the switch demos, and a 10 kΩ@25 °C thermistor. To do: fix fan controller (R1 10 kΩ → ≈ 1 kΩ, R3 600 Ω → ≈ 2.2 kΩ) and re-check V_CE at 80 °C; try BD140 in the switch sims; add an ammeter to compute P = V_CE × I_fan; compare R2 = 276 Ω vs 100 Ω.</t>
         </is>
       </c>
     </row>

--- a/Electricity-Diploma-Episode-Index.xlsx
+++ b/Electricity-Diploma-Episode-Index.xlsx
@@ -1303,7 +1303,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="21">
+    <row r="14" ht="165" customHeight="1" s="21">
       <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Professional Electronic Design Course</t>
@@ -1317,23 +1317,84 @@
           <t>Designing a car-factory circuit for testing fans</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E14" s="28" t="n"/>
-      <c r="F14" s="40" t="n"/>
-      <c r="G14" s="40" t="n"/>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="25" t="n"/>
-      <c r="L14" s="25" t="n"/>
-      <c r="M14" s="25" t="n"/>
-      <c r="N14" s="25" t="n"/>
-      <c r="O14" s="25" t="n"/>
-      <c r="P14" s="25" t="n"/>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>Open README</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>Watch video</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="inlineStr">
+        <is>
+          <t>• R + C in series in a DC circuit = time delay (τ = RC, ≈ 5τ to full)
+• Capacitor charged directly → delayed OFF; resistor before capacitor → delayed ON; series capacitor → self-turn-off pulse
+• Diodes (n × 0.7 V) or Zener (V_Z + 0.7 V) set a fixed threshold the capacitor must reach
+• Staircase-light timer (capacitor holds transistor + relay on)
+• Blocking diode forces the capacitor to discharge only into the transistor base
+• Delay stops the fan flickering on/off when it cools its own sensor</t>
+        </is>
+      </c>
+      <c r="I14" s="25" t="inlineStr">
+        <is>
+          <t>1. Staircase-light timer: 9 V, switch → capacitor → NPN → relay → 220 V lamp (video sim)
+2. 12 V fan, NPN→PNP high-side driver, 470 µF delayed off (hardware)
+3. Divider + 5.1 V Zener delayed on (≈ 4 s start delay, hardware)
+4. Thermistor fan controller + 470 µF + blocking diode (delayed fan turn-off)</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="inlineStr">
+        <is>
+          <t>τ = R·C
+V_C(t) = V_s(1 − e^(−t/RC)); V_C(t) = V_0·e^(−t/RC)
+Threshold = n × 0.7 V (diodes) or V_Z + 0.7 V (5.1 + 0.7 = 5.8 V)
+My sim: τ = 10 kΩ × 470 µF = 4.7 s (with diode); ≈ (1 kΩ ∥ 10 kΩ) × 500 µF ≈ 0.45 s (no diode)</t>
+        </is>
+      </c>
+      <c r="K14" s="25" t="inlineStr">
+        <is>
+          <t>BD140 (PNP), NPN driver, 470 µF timing capacitor, 10 kΩ base resistor, 1 kΩ, LED + 220 Ω, silicon blocking diode, NTC thermistor + 220 Ω (hardware) / 33 kΩ NTC + 1 kΩ (my sim), 5.1 V Zener (variation)</t>
+        </is>
+      </c>
+      <c r="L14" s="25" t="inlineStr">
+        <is>
+          <t>• With diode (470 µF): fan on in &lt; 1 s; after cooling, V_CE(Q2) climbs 8.23 → 11.46 V, LED off after ≈ 13 s, fan settled ≈ 16 s ✔ (est. ≈ 10.5 s from τ = 4.7 s)
+• Without diode (500 µF): off within ≈ 1 s ✔ (τ ≈ 0.45 s)
+• ✘ PNP not saturated when hot: V_CE 7.7–8.2 V, fan gets only ≈ 4 V (driver starved: ≈ 0.1 mA base vs ≈ 45 mA LED branch)</t>
+        </is>
+      </c>
+      <c r="M14" s="25" t="inlineStr">
+        <is>
+          <t>Video sim: 100 µF → no delay, 1000 µF without diode → ≈ 1 s; with diode → much longer
+Hardware: fan keeps running after heat removed until cap empties ✔; without capacitor the fan flickers on/off even with heat present
+Zener variation: ≈ 4 s start delay, stops almost at once</t>
+        </is>
+      </c>
+      <c r="N14" s="25" t="inlineStr">
+        <is>
+          <t>2 simulation GIFs + MP4s: fan delay with blocking diode, fan delay without diode</t>
+        </is>
+      </c>
+      <c r="O14" s="25" t="inlineStr">
+        <is>
+          <t>Adding a capacitor is not enough: check where it discharges. A blocking diode makes the charge go only into the transistor base, so the fan turns on fast but turns off slowly, which also stops it flickering.</t>
+        </is>
+      </c>
+      <c r="P14" s="25" t="inlineStr">
+        <is>
+          <t>Sim used Circuit Wizard 33 kΩ NTC with 1 kΩ bottom resistor (video: ≈ 8 kΩ NTC + 220 Ω). To do: raise LED resistor to ≈ 2.2 kΩ so Q1/Q2 saturate; try 1000 µF / 22 kΩ; build the Zener delayed-on variation.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="21">
       <c r="A15" s="25" t="inlineStr">
@@ -3436,6 +3497,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Electricity-Diploma-Episode-Index.xlsx
+++ b/Electricity-Diploma-Episode-Index.xlsx
@@ -1396,7 +1396,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="21">
+    <row r="15" ht="165" customHeight="1" s="21">
       <c r="A15" s="25" t="inlineStr">
         <is>
           <t>Professional Electronic Design Course</t>
@@ -1410,23 +1410,84 @@
           <t>Designing a useless machine motor circuit</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="40" t="n"/>
-      <c r="G15" s="40" t="n"/>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="25" t="n"/>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="25" t="n"/>
-      <c r="L15" s="25" t="n"/>
-      <c r="M15" s="25" t="n"/>
-      <c r="N15" s="25" t="n"/>
-      <c r="O15" s="25" t="n"/>
-      <c r="P15" s="25" t="n"/>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="n">
+        <v>46325</v>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>Open README</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>Watch video</t>
+        </is>
+      </c>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>• Ground = the point the designer calls 0 V; all ground symbols are one node
+• Voltage of a node depends on the reference (3 / 6 / 9 / 12 V on a 4-resistor divider)
+• Zener + transistor branch needs the tap ≈ V_Z + 0.7 V above the emitter
+• Two batteries in series, midpoint grounded → ± supply (capacitor split fails under load)
+• Complementary NPN/PNP pair steers +V or −V to a motor → direction control
+• NC limit switch in the −V (return) line stops the motor at home</t>
+        </is>
+      </c>
+      <c r="I15" s="25" t="inlineStr">
+        <is>
+          <t>1. 4 × 1 kΩ divider on 12 V, voltmeter reference moved (my sim)
+2. Divider tap → Zener → NPN → LED, ground position moved (video + my sim)
+3. ± supply: two batteries vs. two capacitors (video sim)
+4. Useless machine: ± supply, SPDT switch, 1 kΩ → BC547/BD140 pair, motor, direction LEDs, NC limit switch</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="inlineStr">
+        <is>
+          <t>V_R = 12 V / 4 = 3 V each
+V_on ≈ V_Z + V_BE (+ I_B·R_B)
+V_th = V·R_bottom/(R_top+R_bottom), R_th = R_top ∥ R_bottom
+V_motor ≈ ±(V_s − 0.7 V)
+I_LED ≈ (8.3 − 2) / 220 ≈ 29 mA</t>
+        </is>
+      </c>
+      <c r="K15" s="25" t="inlineStr">
+        <is>
+          <t>BC547 (NPN), BD140 (PNP), 1 kΩ base resistor, 2 batteries (± supply), small 5 V motor + 3 × 100 Ω ∥ series dropper, ON-ON toggle (SPDT), lever micro switch (COM + NC), red + green LEDs with resistors. My sim: ±9 V, 220 Ω LED resistors, 1N751 5.1 V Zener</t>
+        </is>
+      </c>
+      <c r="L15" s="25" t="inlineStr">
+        <is>
+          <t>• Voltmeter on divider: 3.00 / 12.00 / 9.00 / 6.00 V ✔ (exactly 3 V per resistor)
+• Zener LED branch: on with tap 9 V above ground (tap loaded to 7.66 V, I_B ≈ 1.79 mA → V_Z ≈ 5.2 V); off at 3 V and 6 V (needs ≈ 5.8 V, R_th ≈ 667 Ω); on again with D1 moved to top rail
+• Useless machine (±9 V): SW1 up → D1 + forward ✔; down → D2 + reverse ✔; SW2 open → stop ✔</t>
+        </is>
+      </c>
+      <c r="M15" s="25" t="inlineStr">
+        <is>
+          <t>Video sim: tap 3 V → LED off, 6 V → on (3.9 V Zener); with 1.5 V battery in emitter path, 6 V → off, 9 V → on. Capacitor split: ±6 V unloaded, collapses to 0 / −12 V with a 1 kΩ load.
+Hardware: press → red (arm flips switch off) → green (returns) → off at home; works even if re-pressed halfway.</t>
+        </is>
+      </c>
+      <c r="N15" s="25" t="inlineStr">
+        <is>
+          <t>3 simulation GIFs + MP4s: ground reference divider, ground position vs. Zener LED, useless machine with limit switch</t>
+        </is>
+      </c>
+      <c r="O15" s="25" t="inlineStr">
+        <is>
+          <t>Ground is only a reference I choose. A complementary pair lets one signal choose + or − for a motor, and one normally closed switch in the right line (the −V return path only) turns it into a useless machine that stops itself.</t>
+        </is>
+      </c>
+      <c r="P15" s="25" t="inlineStr">
+        <is>
+          <t>Video link: only the playlist is linked; replace with the direct ep13 URL. No .cwz files sent yet. To do: save circuits as .cwz, measure motor voltage, LED resistors → 330 Ω, try 3.9 V Zener in sim 2, simulate capacitor split.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="21">
       <c r="A16" s="25" t="inlineStr">
@@ -3499,6 +3560,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId12"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Electricity-Diploma-Episode-Index.xlsx
+++ b/Electricity-Diploma-Episode-Index.xlsx
@@ -1475,7 +1475,8 @@
       </c>
       <c r="N15" s="25" t="inlineStr">
         <is>
-          <t>3 simulation GIFs + MP4s: ground reference divider, ground position vs. Zener LED, useless machine with limit switch</t>
+          <t>3 simulation GIFs + MP4s: ground reference divider, ground position vs. Zener LED, useless machine with limit switch
+3 circuit files (.cwz): useless machine (final), motor reversing pair (starting circuit), ground position Zener LED</t>
         </is>
       </c>
       <c r="O15" s="25" t="inlineStr">
@@ -1485,7 +1486,7 @@
       </c>
       <c r="P15" s="25" t="inlineStr">
         <is>
-          <t>Video link: only the playlist is linked; replace with the direct ep13 URL. No .cwz files sent yet. To do: save circuits as .cwz, measure motor voltage, LED resistors → 330 Ω, try 3.9 V Zener in sim 2, simulate capacitor split.</t>
+          <t>Sim motor is Circuit Wizard "DC Motor (3V DC)" fed ≈ 8.3 V. To do: add a series dropper resistor for the motor, measure motor voltage, LED resistors → 330 Ω, try 3.9 V Zener in sim 2, simulate capacitor split.</t>
         </is>
       </c>
     </row>

--- a/Electricity-Diploma-Episode-Index.xlsx
+++ b/Electricity-Diploma-Episode-Index.xlsx
@@ -1490,7 +1490,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" s="21">
+    <row r="16" ht="165" customHeight="1" s="21">
       <c r="A16" s="25" t="inlineStr">
         <is>
           <t>Professional Electronic Design Course</t>
@@ -1504,23 +1504,83 @@
           <t>Designing a secret-code circuit without programming</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E16" s="28" t="n"/>
-      <c r="F16" s="40" t="n"/>
-      <c r="G16" s="40" t="n"/>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="25" t="n"/>
-      <c r="L16" s="25" t="n"/>
-      <c r="M16" s="25" t="n"/>
-      <c r="N16" s="25" t="n"/>
-      <c r="O16" s="25" t="n"/>
-      <c r="P16" s="25" t="n"/>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>Open README</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>Watch video</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="inlineStr">
+        <is>
+          <t>• Level 2 intro: circuits that decide on/off by themselves, no programming
+• Switches in series = AND (all must be closed); parallel = OR
+• Wrong switches must actively veto: pull the MOSFET gate to 0 V
+• Pulling a supplied node to ground = battery short → series resistor fixes it
+• MOSFET gate is a capacitor → gate pull-down (10 kΩ–1 MΩ)
+• BJT vs. MOSFET: switching speed, power loss, input drive voltage</t>
+        </is>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t>1. Correct switches 4-5-6-8 in series straight to the solenoid (extra switches ignored ✘)
+2. Series chain → N-MOSFET gate, low-side switch, gate pull-down
+3. Wrong switches ground the gate (works, but shorts the battery ✘)
+4. 10 kΩ series resistor before the gate (final design ✔)
+5. Variants: NPN base version; DIP switch + relay version (code 1-3-6)</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="inlineStr">
+        <is>
+          <t>V_G = 12 × 10k / (10k + 10k) = 6 V
+I_short = 12 V / 10 kΩ = 1.2 mA
+P_BJT = V_CE(sat) × I_C = 0.6 × 0.1 = 60 mW
+P_MOSFET = I_D² × R_DS(on) = 0.1² × 5 = 50 mW</t>
+        </is>
+      </c>
+      <c r="K16" s="25" t="inlineStr">
+        <is>
+          <t>2N7000 N-MOSFET (R_DS(on) ≈ 5 Ω, I_D ≈ 200 mA, V_GS(th) 0.8–3 V), 2 × 10 kΩ (series + gate pull-down), 12 V solenoid lock, flyback diode across the solenoid, 10 latching switches (0–9), 12 V supply. Compared: BC547B (V_CE(sat) 0.2–0.6 V, 100 mA)</t>
+        </is>
+      </c>
+      <c r="L16" s="25" t="inlineStr">
+        <is>
+          <t>Circuit file only (no recording yet): 12 V, ideal N-MOSFET, 6 V DC solenoid, 2 × 10 kΩ, 10 SPST switches. Expected: 4-5-6-8 → gate ≈ 6 V, solenoid on; any extra switch → gate ≈ 0 V, ≈ 1.2 mA</t>
+        </is>
+      </c>
+      <c r="M16" s="25" t="inlineStr">
+        <is>
+          <t>4 → 5 → 6 → 8 → MOSFET on, solenoid pulls in ✔
+Adding 7, 0 or 1 → releases at once ✔
+0, 5, 6, 8 (no 4) → stays locked ✔</t>
+        </is>
+      </c>
+      <c r="N16" s="25" t="inlineStr">
+        <is>
+          <t>1 circuit file (.cwz): secret-code lock (final design)</t>
+        </is>
+      </c>
+      <c r="O16" s="25" t="inlineStr">
+        <is>
+          <t>Series switches make an AND, but a lock must also reject extra inputs: wrong switches pull the gate to 0 V, and one 10 kΩ resistor stops that from shorting the battery. For a 12 V, 100 mA lock a BJT and a MOSFET are equivalent (≈ 60 vs. 50 mW).</t>
+        </is>
+      </c>
+      <c r="P16" s="25" t="inlineStr">
+        <is>
+          <t>Sim uses Circuit Wizard "Solenoid (6V DC)" on 12 V and has no flyback diode. To do: record simulation, measure gate voltage (≈ 6 V) and series-resistor current (≈ 1.2 mA); try without the 10 kΩ / without the pull-down; BC547B version.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="21">
       <c r="A17" s="25" t="inlineStr">
@@ -3563,6 +3623,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId14"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Electricity-Diploma-Episode-Index.xlsx
+++ b/Electricity-Diploma-Episode-Index.xlsx
@@ -1556,7 +1556,12 @@
       </c>
       <c r="L16" s="25" t="inlineStr">
         <is>
-          <t>Circuit file only (no recording yet): 12 V, ideal N-MOSFET, 6 V DC solenoid, 2 × 10 kΩ, 10 SPST switches. Expected: 4-5-6-8 → gate ≈ 6 V, solenoid on; any extra switch → gate ≈ 0 V, ≈ 1.2 mA</t>
+          <t>Code SW4, SW5, SW6, SW8 (SW1–SW10 = digits 1–9, 0), R2 = 10 kΩ series, R1 = 10 kΩ pull-down, ideal N-MOSFET, 6 V solenoid on 12 V:
+• Code only → gate high, solenoid pulled in ✔
+• SW4 opened → gate 0 V, released ✔
+• Code + wrong switch → chain at 12 V up to R2, gate 0 V, released, no short ✔
+• Wrong switch opened → pulled in again ✔
+(No meters: V_G ≈ 6 V and 1.2 mA are calculated)</t>
         </is>
       </c>
       <c r="M16" s="25" t="inlineStr">
@@ -1568,7 +1573,8 @@
       </c>
       <c r="N16" s="25" t="inlineStr">
         <is>
-          <t>1 circuit file (.cwz): secret-code lock (final design)</t>
+          <t>1 simulation GIF + MP4: secret-code lock (code on, code broken, code + wrong switch)
+1 circuit file (.cwz): secret-code lock (final design)</t>
         </is>
       </c>
       <c r="O16" s="25" t="inlineStr">
@@ -1578,7 +1584,7 @@
       </c>
       <c r="P16" s="25" t="inlineStr">
         <is>
-          <t>Sim uses Circuit Wizard "Solenoid (6V DC)" on 12 V and has no flyback diode. To do: record simulation, measure gate voltage (≈ 6 V) and series-resistor current (≈ 1.2 mA); try without the 10 kΩ / without the pull-down; BC547B version.</t>
+          <t>Sim uses Circuit Wizard "Solenoid (6V DC)" on 12 V and has no flyback diode. To do: add a gate voltmeter (≈ 6 V) and an ammeter on R2 (≈ 1.2 mA); try without R2 / without the pull-down; BC547B version.</t>
         </is>
       </c>
     </row>
